--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2438,6 +2438,5176 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122841912</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584384</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6320970</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122851862</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584360</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122841954</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90960</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584450</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6321001</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122839339</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584548</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6320905</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122840491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gränsborg, Gränsborg, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>584478</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6320912</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122851640</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>584396</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6320930</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122851716</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6320935</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122851741</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>584357</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122851575</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>584415</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122851540</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>584425</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6320900</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122842080</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>584434</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122841088</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>584332</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6320935</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122841518</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>584376</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122851562</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>584415</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122852003</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>584646</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6320922</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122851623</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>584406</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6320924</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122851479</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58156</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>584584</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6320910</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122851811</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>584350</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122841878</v>
+      </c>
+      <c r="B34" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>584427</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6320982</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122851869</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>584369</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6320904</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122851927</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>584411</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6320904</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122839920</v>
+      </c>
+      <c r="B37" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>584525</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6320880</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122851504</v>
+      </c>
+      <c r="B38" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>584532</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6320881</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122840279</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6320836</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122851605</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>584395</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122851829</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>584348</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122851469</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>584584</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6320910</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122841596</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>584389</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6320931</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122841069</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>584349</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6320925</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122851724</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>584375</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6320924</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122841328</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>584336</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6320932</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122841409</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>584384</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6320921</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122841582</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>584345</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6320948</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122841533</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>584369</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6320926</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122851662</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>584391</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6320923</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122851599</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>584395</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122852007</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>584646</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6320922</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122851735</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>584357</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122851756</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>584359</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6320919</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122839190</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>584581</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6320913</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122851590</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>584409</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6320920</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122841855</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6320986</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122840797</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Spetalehult, Spetalehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>584406</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6320860</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122840605</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>584384</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6320873</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122851783</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>584336</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6320920</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122841912</v>
+        <v>122851640</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,55 +2452,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584384</v>
+        <v>584396</v>
       </c>
       <c r="R16" t="n">
-        <v>6320970</v>
+        <v>6320930</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2527,39 +2521,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851862</v>
+        <v>122851504</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>95126</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2568,32 +2573,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -2604,10 +2605,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584360</v>
+        <v>584532</v>
       </c>
       <c r="R17" t="n">
-        <v>6320915</v>
+        <v>6320881</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2677,10 +2678,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841954</v>
+        <v>122851479</v>
       </c>
       <c r="B18" t="n">
-        <v>90960</v>
+        <v>58156</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2689,45 +2690,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584450</v>
+        <v>584584</v>
       </c>
       <c r="R18" t="n">
-        <v>6321001</v>
+        <v>6320910</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2754,9 +2763,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,22 +2790,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122839339</v>
+        <v>122851741</v>
       </c>
       <c r="B19" t="n">
-        <v>95118</v>
+        <v>57848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2799,37 +2818,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584548</v>
+        <v>584357</v>
       </c>
       <c r="R19" t="n">
-        <v>6320905</v>
+        <v>6320937</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2856,9 +2887,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2873,22 +2914,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122840491</v>
+        <v>122851540</v>
       </c>
       <c r="B20" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2897,41 +2938,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584478</v>
+        <v>584425</v>
       </c>
       <c r="R20" t="n">
-        <v>6320912</v>
+        <v>6320900</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2958,39 +3007,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851640</v>
+        <v>122851575</v>
       </c>
       <c r="B21" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2999,30 +3059,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -3035,10 +3095,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584396</v>
+        <v>584415</v>
       </c>
       <c r="R21" t="n">
-        <v>6320930</v>
+        <v>6320915</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3108,10 +3168,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851716</v>
+        <v>122851469</v>
       </c>
       <c r="B22" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,7 +3203,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3156,10 +3216,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R22" t="n">
-        <v>6320935</v>
+        <v>6320910</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3229,10 +3289,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851741</v>
+        <v>122841855</v>
       </c>
       <c r="B23" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3241,53 +3301,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R23" t="n">
-        <v>6320937</v>
+        <v>6320986</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3314,19 +3362,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,22 +3379,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851575</v>
+        <v>122841328</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3386,28 +3424,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584415</v>
+        <v>584336</v>
       </c>
       <c r="R24" t="n">
-        <v>6320915</v>
+        <v>6320932</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3434,19 +3464,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3455,29 +3480,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851540</v>
+        <v>122841088</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3509,26 +3533,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584425</v>
+        <v>584332</v>
       </c>
       <c r="R25" t="n">
-        <v>6320900</v>
+        <v>6320935</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3555,50 +3585,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842080</v>
+        <v>122841596</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3607,25 +3626,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3635,13 +3654,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584434</v>
+        <v>584389</v>
       </c>
       <c r="R26" t="n">
-        <v>6320937</v>
+        <v>6320931</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3671,6 +3690,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3697,10 +3721,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841088</v>
+        <v>122841533</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,34 +3754,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584332</v>
+        <v>584369</v>
       </c>
       <c r="R27" t="n">
-        <v>6320935</v>
+        <v>6320926</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3787,6 +3797,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3801,22 +3816,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841518</v>
+        <v>122851605</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3825,55 +3840,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584376</v>
+        <v>584395</v>
       </c>
       <c r="R28" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3900,39 +3909,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851562</v>
+        <v>122852007</v>
       </c>
       <c r="B29" t="n">
-        <v>105453</v>
+        <v>57484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3941,35 +3961,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3977,10 +4001,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584415</v>
+        <v>584646</v>
       </c>
       <c r="R29" t="n">
-        <v>6320915</v>
+        <v>6320922</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4031,7 +4055,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4050,10 +4073,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122852003</v>
+        <v>122851862</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4062,39 +4085,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4102,10 +4121,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584646</v>
+        <v>584360</v>
       </c>
       <c r="R30" t="n">
-        <v>6320922</v>
+        <v>6320915</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4156,6 +4175,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4174,10 +4194,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851623</v>
+        <v>122851756</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4209,7 +4229,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4222,10 +4242,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584406</v>
+        <v>584359</v>
       </c>
       <c r="R31" t="n">
-        <v>6320924</v>
+        <v>6320919</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4295,10 +4315,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851479</v>
+        <v>122840279</v>
       </c>
       <c r="B32" t="n">
-        <v>58156</v>
+        <v>105461</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4311,49 +4331,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103044</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R32" t="n">
-        <v>6320910</v>
+        <v>6320836</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4380,19 +4392,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4407,22 +4409,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851811</v>
+        <v>122851724</v>
       </c>
       <c r="B33" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4454,7 +4456,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4467,10 +4469,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584350</v>
+        <v>584375</v>
       </c>
       <c r="R33" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4540,10 +4542,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122841878</v>
+        <v>122851829</v>
       </c>
       <c r="B34" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4552,41 +4554,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584427</v>
+        <v>584348</v>
       </c>
       <c r="R34" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4613,39 +4623,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851869</v>
+        <v>122851783</v>
       </c>
       <c r="B35" t="n">
-        <v>98347</v>
+        <v>57369</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4654,35 +4675,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4690,10 +4715,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584369</v>
+        <v>584336</v>
       </c>
       <c r="R35" t="n">
-        <v>6320904</v>
+        <v>6320920</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4744,7 +4769,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4763,10 +4787,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851927</v>
+        <v>122841518</v>
       </c>
       <c r="B36" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4798,26 +4822,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584411</v>
+        <v>584376</v>
       </c>
       <c r="R36" t="n">
-        <v>6320904</v>
+        <v>6320937</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4844,50 +4874,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122839920</v>
+        <v>122841069</v>
       </c>
       <c r="B37" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4896,25 +4915,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4924,10 +4943,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584525</v>
+        <v>584349</v>
       </c>
       <c r="R37" t="n">
-        <v>6320880</v>
+        <v>6320925</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4964,7 +4983,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4991,10 +5010,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851504</v>
+        <v>122851735</v>
       </c>
       <c r="B38" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5003,28 +5022,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -5035,10 +5058,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584532</v>
+        <v>584357</v>
       </c>
       <c r="R38" t="n">
-        <v>6320881</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5108,10 +5131,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122840279</v>
+        <v>122852003</v>
       </c>
       <c r="B39" t="n">
-        <v>105453</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5120,45 +5143,53 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584419</v>
+        <v>584646</v>
       </c>
       <c r="R39" t="n">
-        <v>6320836</v>
+        <v>6320922</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5185,9 +5216,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5202,22 +5243,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851605</v>
+        <v>122840491</v>
       </c>
       <c r="B40" t="n">
-        <v>105453</v>
+        <v>95126</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5230,45 +5271,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584395</v>
+        <v>584478</v>
       </c>
       <c r="R40" t="n">
-        <v>6320916</v>
+        <v>6320912</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,50 +5328,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851829</v>
+        <v>122851623</v>
       </c>
       <c r="B41" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5370,7 +5392,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5383,10 +5405,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584348</v>
+        <v>584406</v>
       </c>
       <c r="R41" t="n">
-        <v>6320915</v>
+        <v>6320924</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5456,10 +5478,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851469</v>
+        <v>122839920</v>
       </c>
       <c r="B42" t="n">
-        <v>98347</v>
+        <v>95126</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5468,49 +5490,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584584</v>
+        <v>584525</v>
       </c>
       <c r="R42" t="n">
-        <v>6320910</v>
+        <v>6320880</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5537,19 +5551,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5558,29 +5567,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122841596</v>
+        <v>122839339</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>95126</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5589,41 +5597,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584389</v>
+        <v>584548</v>
       </c>
       <c r="R43" t="n">
-        <v>6320931</v>
+        <v>6320905</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5653,11 +5661,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5672,22 +5675,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841069</v>
+        <v>122842080</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5720,17 +5723,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584349</v>
+        <v>584434</v>
       </c>
       <c r="R44" t="n">
-        <v>6320925</v>
+        <v>6320937</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5760,11 +5763,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5791,10 +5789,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851724</v>
+        <v>122851811</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5826,7 +5824,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5839,10 +5837,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584375</v>
+        <v>584350</v>
       </c>
       <c r="R45" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5912,10 +5910,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841328</v>
+        <v>122851590</v>
       </c>
       <c r="B46" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5945,20 +5943,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584336</v>
+        <v>584409</v>
       </c>
       <c r="R46" t="n">
-        <v>6320932</v>
+        <v>6320920</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,14 +5991,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6001,18 +6012,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6126,10 +6138,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841582</v>
+        <v>122851562</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6138,55 +6150,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584345</v>
+        <v>584415</v>
       </c>
       <c r="R48" t="n">
-        <v>6320948</v>
+        <v>6320915</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6213,39 +6219,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841533</v>
+        <v>122840797</v>
       </c>
       <c r="B49" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6278,17 +6295,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584369</v>
+        <v>584406</v>
       </c>
       <c r="R49" t="n">
-        <v>6320926</v>
+        <v>6320860</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6318,11 +6335,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6337,22 +6349,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851662</v>
+        <v>122840605</v>
       </c>
       <c r="B50" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6382,28 +6394,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584391</v>
+        <v>584384</v>
       </c>
       <c r="R50" t="n">
-        <v>6320923</v>
+        <v>6320873</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6430,50 +6434,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851599</v>
+        <v>122839190</v>
       </c>
       <c r="B51" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6503,28 +6496,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584395</v>
+        <v>584581</v>
       </c>
       <c r="R51" t="n">
-        <v>6320916</v>
+        <v>6320913</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6551,50 +6536,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122852007</v>
+        <v>122851869</v>
       </c>
       <c r="B52" t="n">
-        <v>57484</v>
+        <v>98355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6603,39 +6577,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6643,10 +6613,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584646</v>
+        <v>584369</v>
       </c>
       <c r="R52" t="n">
-        <v>6320922</v>
+        <v>6320904</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6697,6 +6667,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6715,10 +6686,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851735</v>
+        <v>122851662</v>
       </c>
       <c r="B53" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6750,7 +6721,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6763,10 +6734,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584357</v>
+        <v>584391</v>
       </c>
       <c r="R53" t="n">
-        <v>6320937</v>
+        <v>6320923</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6836,10 +6807,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851756</v>
+        <v>122841954</v>
       </c>
       <c r="B54" t="n">
-        <v>98347</v>
+        <v>90964</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6848,49 +6819,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584359</v>
+        <v>584450</v>
       </c>
       <c r="R54" t="n">
-        <v>6320919</v>
+        <v>6321001</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6917,50 +6884,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122839190</v>
+        <v>122841912</v>
       </c>
       <c r="B55" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6990,20 +6946,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584581</v>
+        <v>584384</v>
       </c>
       <c r="R55" t="n">
-        <v>6320913</v>
+        <v>6320970</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7047,22 +7017,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851590</v>
+        <v>122851599</v>
       </c>
       <c r="B56" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7094,7 +7064,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -7107,10 +7077,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584409</v>
+        <v>584395</v>
       </c>
       <c r="R56" t="n">
-        <v>6320920</v>
+        <v>6320916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7180,10 +7150,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841855</v>
+        <v>122851927</v>
       </c>
       <c r="B57" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7213,20 +7183,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584419</v>
+        <v>584411</v>
       </c>
       <c r="R57" t="n">
-        <v>6320986</v>
+        <v>6320904</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7253,39 +7231,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840797</v>
+        <v>122851716</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7315,20 +7304,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584406</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320860</v>
+        <v>6320935</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7355,39 +7352,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122840605</v>
+        <v>122841582</v>
       </c>
       <c r="B59" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7417,20 +7425,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584384</v>
+        <v>584345</v>
       </c>
       <c r="R59" t="n">
-        <v>6320873</v>
+        <v>6320948</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7474,22 +7496,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851783</v>
+        <v>122841878</v>
       </c>
       <c r="B60" t="n">
-        <v>57369</v>
+        <v>105461</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7498,53 +7520,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584336</v>
+        <v>584427</v>
       </c>
       <c r="R60" t="n">
-        <v>6320920</v>
+        <v>6320982</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7571,19 +7581,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7598,12 +7598,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851504</v>
+        <v>122851741</v>
       </c>
       <c r="B17" t="n">
-        <v>95126</v>
+        <v>57848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2577,27 +2577,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2605,10 +2613,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584532</v>
+        <v>584357</v>
       </c>
       <c r="R17" t="n">
-        <v>6320881</v>
+        <v>6320937</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2659,7 +2667,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2678,10 +2685,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851479</v>
+        <v>122851504</v>
       </c>
       <c r="B18" t="n">
-        <v>58156</v>
+        <v>95126</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2694,35 +2701,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2730,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584584</v>
+        <v>584532</v>
       </c>
       <c r="R18" t="n">
-        <v>6320910</v>
+        <v>6320881</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2784,6 +2783,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851741</v>
+        <v>122851479</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>58156</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2818,16 +2818,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2837,14 +2837,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584357</v>
+        <v>584584</v>
       </c>
       <c r="R19" t="n">
-        <v>6320937</v>
+        <v>6320910</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -3614,10 +3614,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841596</v>
+        <v>122841533</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3626,38 +3626,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584389</v>
+        <v>584369</v>
       </c>
       <c r="R26" t="n">
-        <v>6320931</v>
+        <v>6320926</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841533</v>
+        <v>122841596</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3733,38 +3733,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584369</v>
+        <v>584389</v>
       </c>
       <c r="R27" t="n">
-        <v>6320926</v>
+        <v>6320931</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>100-tal plantor</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851640</v>
+        <v>122851504</v>
       </c>
       <c r="B16" t="n">
-        <v>105461</v>
+        <v>95126</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2456,28 +2456,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -2488,10 +2484,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584396</v>
+        <v>584532</v>
       </c>
       <c r="R16" t="n">
-        <v>6320930</v>
+        <v>6320881</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2561,10 +2557,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851741</v>
+        <v>122851623</v>
       </c>
       <c r="B17" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,39 +2569,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2613,10 +2605,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584357</v>
+        <v>584406</v>
       </c>
       <c r="R17" t="n">
-        <v>6320937</v>
+        <v>6320924</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2667,6 +2659,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2685,10 +2678,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851504</v>
+        <v>122841954</v>
       </c>
       <c r="B18" t="n">
-        <v>95126</v>
+        <v>90964</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2697,45 +2690,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584532</v>
+        <v>584450</v>
       </c>
       <c r="R18" t="n">
-        <v>6320881</v>
+        <v>6321001</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2762,50 +2755,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851479</v>
+        <v>122851927</v>
       </c>
       <c r="B19" t="n">
-        <v>58156</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2814,39 +2796,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2854,10 +2832,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584584</v>
+        <v>584411</v>
       </c>
       <c r="R19" t="n">
-        <v>6320910</v>
+        <v>6320904</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2908,6 +2886,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2926,10 +2905,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851540</v>
+        <v>122851605</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2938,30 +2917,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2974,10 +2953,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584425</v>
+        <v>584395</v>
       </c>
       <c r="R20" t="n">
-        <v>6320900</v>
+        <v>6320916</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3047,7 +3026,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851575</v>
+        <v>122841518</v>
       </c>
       <c r="B21" t="n">
         <v>98355</v>
@@ -3082,26 +3061,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584415</v>
+        <v>584376</v>
       </c>
       <c r="R21" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3128,47 +3113,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851469</v>
+        <v>122840605</v>
       </c>
       <c r="B22" t="n">
         <v>98355</v>
@@ -3201,28 +3175,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584584</v>
+        <v>584384</v>
       </c>
       <c r="R22" t="n">
-        <v>6320910</v>
+        <v>6320873</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3249,50 +3215,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841855</v>
+        <v>122840491</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>95126</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3301,41 +3256,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584419</v>
+        <v>584478</v>
       </c>
       <c r="R23" t="n">
-        <v>6320986</v>
+        <v>6320912</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3379,19 +3334,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841328</v>
+        <v>122841069</v>
       </c>
       <c r="B24" t="n">
         <v>98355</v>
@@ -3431,10 +3386,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584336</v>
+        <v>584349</v>
       </c>
       <c r="R24" t="n">
-        <v>6320932</v>
+        <v>6320925</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3471,7 +3426,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>40-tal plantor</t>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3498,10 +3453,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841088</v>
+        <v>122841409</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3510,55 +3465,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584332</v>
+        <v>584384</v>
       </c>
       <c r="R25" t="n">
-        <v>6320935</v>
+        <v>6320921</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3602,19 +3548,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841533</v>
+        <v>122851540</v>
       </c>
       <c r="B26" t="n">
         <v>98355</v>
@@ -3647,20 +3593,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584369</v>
+        <v>584425</v>
       </c>
       <c r="R26" t="n">
-        <v>6320926</v>
+        <v>6320900</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3687,14 +3641,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3703,28 +3662,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841596</v>
+        <v>122851862</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3733,41 +3693,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584389</v>
+        <v>584360</v>
       </c>
       <c r="R27" t="n">
-        <v>6320931</v>
+        <v>6320915</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3794,14 +3762,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3810,28 +3783,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851605</v>
+        <v>122839339</v>
       </c>
       <c r="B28" t="n">
-        <v>105461</v>
+        <v>95126</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3844,45 +3818,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584395</v>
+        <v>584548</v>
       </c>
       <c r="R28" t="n">
-        <v>6320916</v>
+        <v>6320905</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3909,50 +3875,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122852007</v>
+        <v>122851869</v>
       </c>
       <c r="B29" t="n">
-        <v>57484</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3961,39 +3916,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4001,10 +3952,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584646</v>
+        <v>584369</v>
       </c>
       <c r="R29" t="n">
-        <v>6320922</v>
+        <v>6320904</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4055,6 +4006,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4073,10 +4025,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851862</v>
+        <v>122841596</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4085,49 +4037,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584360</v>
+        <v>584389</v>
       </c>
       <c r="R30" t="n">
-        <v>6320915</v>
+        <v>6320931</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4154,19 +4098,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4175,29 +4114,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851756</v>
+        <v>122839920</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>95126</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4206,49 +4144,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584359</v>
+        <v>584525</v>
       </c>
       <c r="R31" t="n">
-        <v>6320919</v>
+        <v>6320880</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4275,19 +4205,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4296,29 +4221,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122840279</v>
+        <v>122851599</v>
       </c>
       <c r="B32" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4327,45 +4251,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584419</v>
+        <v>584395</v>
       </c>
       <c r="R32" t="n">
-        <v>6320836</v>
+        <v>6320916</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4392,36 +4320,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851724</v>
+        <v>122851469</v>
       </c>
       <c r="B33" t="n">
         <v>98355</v>
@@ -4456,7 +4395,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4469,10 +4408,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584375</v>
+        <v>584584</v>
       </c>
       <c r="R33" t="n">
-        <v>6320924</v>
+        <v>6320910</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4542,7 +4481,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851829</v>
+        <v>122841088</v>
       </c>
       <c r="B34" t="n">
         <v>98355</v>
@@ -4577,26 +4516,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584348</v>
+        <v>584332</v>
       </c>
       <c r="R34" t="n">
-        <v>6320915</v>
+        <v>6320935</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4623,50 +4568,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851783</v>
+        <v>122851756</v>
       </c>
       <c r="B35" t="n">
-        <v>57369</v>
+        <v>98355</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4675,39 +4609,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4715,10 +4645,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584336</v>
+        <v>584359</v>
       </c>
       <c r="R35" t="n">
-        <v>6320920</v>
+        <v>6320919</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4769,6 +4699,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4787,7 +4718,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841518</v>
+        <v>122851716</v>
       </c>
       <c r="B36" t="n">
         <v>98355</v>
@@ -4822,32 +4753,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584376</v>
+        <v>584419</v>
       </c>
       <c r="R36" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4874,39 +4799,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841069</v>
+        <v>122851783</v>
       </c>
       <c r="B37" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4915,41 +4851,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584349</v>
+        <v>584336</v>
       </c>
       <c r="R37" t="n">
-        <v>6320925</v>
+        <v>6320920</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4976,14 +4924,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,19 +4951,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851735</v>
+        <v>122851590</v>
       </c>
       <c r="B38" t="n">
         <v>98355</v>
@@ -5045,7 +4998,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5058,10 +5011,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584357</v>
+        <v>584409</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320920</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5131,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122852003</v>
+        <v>122840797</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5143,53 +5096,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584646</v>
+        <v>584406</v>
       </c>
       <c r="R39" t="n">
-        <v>6320922</v>
+        <v>6320860</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5216,19 +5157,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5243,22 +5174,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122840491</v>
+        <v>122842080</v>
       </c>
       <c r="B40" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5267,38 +5198,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584478</v>
+        <v>584434</v>
       </c>
       <c r="R40" t="n">
-        <v>6320912</v>
+        <v>6320937</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5345,22 +5276,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851623</v>
+        <v>122851741</v>
       </c>
       <c r="B41" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5369,35 +5300,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5405,10 +5340,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584406</v>
+        <v>584357</v>
       </c>
       <c r="R41" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5459,7 +5394,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5478,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122839920</v>
+        <v>122841912</v>
       </c>
       <c r="B42" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5490,41 +5424,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584525</v>
+        <v>584384</v>
       </c>
       <c r="R42" t="n">
-        <v>6320880</v>
+        <v>6320970</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5554,11 +5502,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5573,22 +5516,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122839339</v>
+        <v>122841533</v>
       </c>
       <c r="B43" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5597,41 +5540,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584548</v>
+        <v>584369</v>
       </c>
       <c r="R43" t="n">
-        <v>6320905</v>
+        <v>6320926</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5661,6 +5604,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5675,22 +5623,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122842080</v>
+        <v>122852007</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>57484</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5699,41 +5647,53 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584434</v>
+        <v>584646</v>
       </c>
       <c r="R44" t="n">
-        <v>6320937</v>
+        <v>6320922</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5760,9 +5720,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5777,19 +5747,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851811</v>
+        <v>122841855</v>
       </c>
       <c r="B45" t="n">
         <v>98355</v>
@@ -5822,28 +5792,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584350</v>
+        <v>584419</v>
       </c>
       <c r="R45" t="n">
-        <v>6320916</v>
+        <v>6320986</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5870,47 +5832,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851590</v>
+        <v>122841328</v>
       </c>
       <c r="B46" t="n">
         <v>98355</v>
@@ -5943,28 +5894,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584409</v>
+        <v>584336</v>
       </c>
       <c r="R46" t="n">
-        <v>6320920</v>
+        <v>6320932</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5991,19 +5934,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6012,29 +5950,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841409</v>
+        <v>122851662</v>
       </c>
       <c r="B47" t="n">
-        <v>57369</v>
+        <v>98355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6043,43 +5980,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584384</v>
+        <v>584391</v>
       </c>
       <c r="R47" t="n">
-        <v>6320921</v>
+        <v>6320923</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6109,39 +6049,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851562</v>
+        <v>122851735</v>
       </c>
       <c r="B48" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6150,30 +6101,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6186,10 +6137,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584415</v>
+        <v>584357</v>
       </c>
       <c r="R48" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6259,7 +6210,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122840797</v>
+        <v>122851724</v>
       </c>
       <c r="B49" t="n">
         <v>98355</v>
@@ -6292,20 +6243,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584406</v>
+        <v>584375</v>
       </c>
       <c r="R49" t="n">
-        <v>6320860</v>
+        <v>6320924</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6332,36 +6291,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122840605</v>
+        <v>122851829</v>
       </c>
       <c r="B50" t="n">
         <v>98355</v>
@@ -6394,20 +6364,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584384</v>
+        <v>584348</v>
       </c>
       <c r="R50" t="n">
-        <v>6320873</v>
+        <v>6320915</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6434,39 +6412,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122839190</v>
+        <v>122851479</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>58156</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6475,41 +6464,53 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584581</v>
+        <v>584584</v>
       </c>
       <c r="R51" t="n">
-        <v>6320913</v>
+        <v>6320910</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6536,9 +6537,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6553,19 +6564,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851869</v>
+        <v>122839190</v>
       </c>
       <c r="B52" t="n">
         <v>98355</v>
@@ -6598,28 +6609,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584369</v>
+        <v>584581</v>
       </c>
       <c r="R52" t="n">
-        <v>6320904</v>
+        <v>6320913</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6646,50 +6649,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851662</v>
+        <v>122841878</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6698,49 +6690,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584391</v>
+        <v>584427</v>
       </c>
       <c r="R53" t="n">
-        <v>6320923</v>
+        <v>6320982</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6767,50 +6751,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122841954</v>
+        <v>122851640</v>
       </c>
       <c r="B54" t="n">
-        <v>90964</v>
+        <v>105461</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6819,45 +6792,49 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584450</v>
+        <v>584396</v>
       </c>
       <c r="R54" t="n">
-        <v>6321001</v>
+        <v>6320930</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6884,36 +6861,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841912</v>
+        <v>122851575</v>
       </c>
       <c r="B55" t="n">
         <v>98355</v>
@@ -6948,32 +6936,26 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584384</v>
+        <v>584415</v>
       </c>
       <c r="R55" t="n">
-        <v>6320970</v>
+        <v>6320915</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7000,36 +6982,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851599</v>
+        <v>122841582</v>
       </c>
       <c r="B56" t="n">
         <v>98355</v>
@@ -7064,26 +7057,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584395</v>
+        <v>584345</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320948</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7110,50 +7109,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851927</v>
+        <v>122840279</v>
       </c>
       <c r="B57" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7162,49 +7150,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584411</v>
+        <v>584419</v>
       </c>
       <c r="R57" t="n">
-        <v>6320904</v>
+        <v>6320836</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7231,50 +7215,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851716</v>
+        <v>122852003</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7283,35 +7256,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7319,10 +7296,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584646</v>
       </c>
       <c r="R58" t="n">
-        <v>6320935</v>
+        <v>6320922</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7373,7 +7350,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7392,7 +7368,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841582</v>
+        <v>122851811</v>
       </c>
       <c r="B59" t="n">
         <v>98355</v>
@@ -7427,32 +7403,26 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584345</v>
+        <v>584350</v>
       </c>
       <c r="R59" t="n">
-        <v>6320948</v>
+        <v>6320916</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7479,36 +7449,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122841878</v>
+        <v>122851562</v>
       </c>
       <c r="B60" t="n">
         <v>105461</v>
@@ -7541,20 +7522,28 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584427</v>
+        <v>584415</v>
       </c>
       <c r="R60" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7581,29 +7570,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851504</v>
+        <v>122851599</v>
       </c>
       <c r="B16" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,28 +2452,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -2484,10 +2488,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R16" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2557,10 +2561,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851623</v>
+        <v>122841533</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2590,28 +2594,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584406</v>
+        <v>584369</v>
       </c>
       <c r="R17" t="n">
-        <v>6320924</v>
+        <v>6320926</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2638,19 +2634,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2659,29 +2650,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841954</v>
+        <v>122842080</v>
       </c>
       <c r="B18" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2690,42 +2680,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584450</v>
+        <v>584434</v>
       </c>
       <c r="R18" t="n">
-        <v>6321001</v>
+        <v>6320937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2772,22 +2758,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851927</v>
+        <v>122841596</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2796,49 +2782,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584411</v>
+        <v>584389</v>
       </c>
       <c r="R19" t="n">
-        <v>6320904</v>
+        <v>6320931</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2865,19 +2843,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,29 +2859,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851605</v>
+        <v>122851756</v>
       </c>
       <c r="B20" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2917,30 +2889,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2953,10 +2925,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584395</v>
+        <v>584359</v>
       </c>
       <c r="R20" t="n">
-        <v>6320916</v>
+        <v>6320919</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3026,10 +2998,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841518</v>
+        <v>122841328</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3059,34 +3031,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584376</v>
+        <v>584336</v>
       </c>
       <c r="R21" t="n">
-        <v>6320937</v>
+        <v>6320932</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3116,6 +3074,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,22 +3093,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840605</v>
+        <v>122841069</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3182,13 +3145,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584384</v>
+        <v>584349</v>
       </c>
       <c r="R22" t="n">
-        <v>6320873</v>
+        <v>6320925</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3218,6 +3181,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3244,10 +3212,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840491</v>
+        <v>122851575</v>
       </c>
       <c r="B23" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3256,41 +3224,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584478</v>
+        <v>584415</v>
       </c>
       <c r="R23" t="n">
-        <v>6320912</v>
+        <v>6320915</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3317,39 +3293,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841069</v>
+        <v>122851469</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3379,20 +3366,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584349</v>
+        <v>584584</v>
       </c>
       <c r="R24" t="n">
-        <v>6320925</v>
+        <v>6320910</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3419,14 +3414,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3435,28 +3435,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841409</v>
+        <v>122851562</v>
       </c>
       <c r="B25" t="n">
-        <v>57369</v>
+        <v>105463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3465,43 +3466,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584384</v>
+        <v>584415</v>
       </c>
       <c r="R25" t="n">
-        <v>6320921</v>
+        <v>6320915</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3531,39 +3535,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851540</v>
+        <v>122841518</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3595,26 +3610,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584425</v>
+        <v>584376</v>
       </c>
       <c r="R26" t="n">
-        <v>6320900</v>
+        <v>6320937</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3641,50 +3662,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851862</v>
+        <v>122840279</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3693,49 +3703,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584360</v>
+        <v>584419</v>
       </c>
       <c r="R27" t="n">
-        <v>6320915</v>
+        <v>6320836</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3762,50 +3768,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122839339</v>
+        <v>122840491</v>
       </c>
       <c r="B28" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3838,17 +3833,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584548</v>
+        <v>584478</v>
       </c>
       <c r="R28" t="n">
-        <v>6320905</v>
+        <v>6320912</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3904,10 +3899,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851869</v>
+        <v>122851862</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3939,7 +3934,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3952,10 +3947,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584369</v>
+        <v>584360</v>
       </c>
       <c r="R29" t="n">
-        <v>6320904</v>
+        <v>6320915</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4025,10 +4020,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841596</v>
+        <v>122851590</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4037,41 +4032,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584389</v>
+        <v>584409</v>
       </c>
       <c r="R30" t="n">
-        <v>6320931</v>
+        <v>6320920</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4098,14 +4101,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4114,28 +4122,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122839920</v>
+        <v>122851716</v>
       </c>
       <c r="B31" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4144,41 +4153,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584525</v>
+        <v>584419</v>
       </c>
       <c r="R31" t="n">
-        <v>6320880</v>
+        <v>6320935</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4205,14 +4222,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4221,28 +4243,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851599</v>
+        <v>122841582</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4274,26 +4297,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584395</v>
+        <v>584345</v>
       </c>
       <c r="R32" t="n">
-        <v>6320916</v>
+        <v>6320948</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4320,50 +4349,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851469</v>
+        <v>122841855</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,28 +4411,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R33" t="n">
-        <v>6320910</v>
+        <v>6320986</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4441,50 +4451,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122841088</v>
+        <v>122851724</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4516,32 +4515,26 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584332</v>
+        <v>584375</v>
       </c>
       <c r="R34" t="n">
-        <v>6320935</v>
+        <v>6320924</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4568,39 +4561,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851756</v>
+        <v>122851662</v>
       </c>
       <c r="B35" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4632,7 +4636,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4645,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584359</v>
+        <v>584391</v>
       </c>
       <c r="R35" t="n">
-        <v>6320919</v>
+        <v>6320923</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4718,10 +4722,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851716</v>
+        <v>122851829</v>
       </c>
       <c r="B36" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4753,7 +4757,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -4766,10 +4770,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584419</v>
+        <v>584348</v>
       </c>
       <c r="R36" t="n">
-        <v>6320935</v>
+        <v>6320915</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4839,10 +4843,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851783</v>
+        <v>122851741</v>
       </c>
       <c r="B37" t="n">
-        <v>57369</v>
+        <v>57848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4851,20 +4855,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100001</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4874,14 +4878,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4891,10 +4895,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584336</v>
+        <v>584357</v>
       </c>
       <c r="R37" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4963,10 +4967,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851590</v>
+        <v>122840797</v>
       </c>
       <c r="B38" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4996,28 +5000,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584409</v>
+        <v>584406</v>
       </c>
       <c r="R38" t="n">
-        <v>6320920</v>
+        <v>6320860</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5044,50 +5040,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122840797</v>
+        <v>122851811</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5117,20 +5102,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584406</v>
+        <v>584350</v>
       </c>
       <c r="R39" t="n">
-        <v>6320860</v>
+        <v>6320916</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5157,39 +5150,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842080</v>
+        <v>122851927</v>
       </c>
       <c r="B40" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5219,20 +5223,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584434</v>
+        <v>584411</v>
       </c>
       <c r="R40" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5259,39 +5271,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851741</v>
+        <v>122841088</v>
       </c>
       <c r="B41" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5300,53 +5323,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584357</v>
+        <v>584332</v>
       </c>
       <c r="R41" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5373,19 +5398,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5400,22 +5415,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841912</v>
+        <v>122841878</v>
       </c>
       <c r="B42" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5424,52 +5439,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584384</v>
+        <v>584427</v>
       </c>
       <c r="R42" t="n">
-        <v>6320970</v>
+        <v>6320982</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5516,22 +5517,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122841533</v>
+        <v>122852007</v>
       </c>
       <c r="B43" t="n">
-        <v>98355</v>
+        <v>57484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5540,41 +5541,53 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584369</v>
+        <v>584646</v>
       </c>
       <c r="R43" t="n">
-        <v>6320926</v>
+        <v>6320922</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5601,14 +5614,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5623,22 +5641,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122852007</v>
+        <v>122851504</v>
       </c>
       <c r="B44" t="n">
-        <v>57484</v>
+        <v>95128</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5647,39 +5665,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5687,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584646</v>
+        <v>584532</v>
       </c>
       <c r="R44" t="n">
-        <v>6320922</v>
+        <v>6320881</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5741,6 +5751,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5759,10 +5770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841855</v>
+        <v>122851640</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,41 +5782,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584419</v>
+        <v>584396</v>
       </c>
       <c r="R45" t="n">
-        <v>6320986</v>
+        <v>6320930</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5832,39 +5851,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841328</v>
+        <v>122851623</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5894,20 +5924,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584336</v>
+        <v>584406</v>
       </c>
       <c r="R46" t="n">
-        <v>6320932</v>
+        <v>6320924</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5934,14 +5972,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5950,28 +5993,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851662</v>
+        <v>122839190</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6001,28 +6045,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584391</v>
+        <v>584581</v>
       </c>
       <c r="R47" t="n">
-        <v>6320923</v>
+        <v>6320913</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6049,50 +6085,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851735</v>
+        <v>122839339</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6101,49 +6126,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584357</v>
+        <v>584548</v>
       </c>
       <c r="R48" t="n">
-        <v>6320937</v>
+        <v>6320905</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6170,50 +6187,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851724</v>
+        <v>122841954</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>90964</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6222,49 +6228,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584375</v>
+        <v>584450</v>
       </c>
       <c r="R49" t="n">
-        <v>6320924</v>
+        <v>6321001</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6291,50 +6293,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851829</v>
+        <v>122851869</v>
       </c>
       <c r="B50" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6366,7 +6357,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6379,10 +6370,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584348</v>
+        <v>584369</v>
       </c>
       <c r="R50" t="n">
-        <v>6320915</v>
+        <v>6320904</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6452,10 +6443,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851479</v>
+        <v>122851605</v>
       </c>
       <c r="B51" t="n">
-        <v>58156</v>
+        <v>105463</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6468,35 +6459,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103044</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6504,10 +6491,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584584</v>
+        <v>584395</v>
       </c>
       <c r="R51" t="n">
-        <v>6320910</v>
+        <v>6320916</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6558,6 +6545,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6576,10 +6564,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122839190</v>
+        <v>122839920</v>
       </c>
       <c r="B52" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6588,25 +6576,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6616,10 +6604,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584581</v>
+        <v>584525</v>
       </c>
       <c r="R52" t="n">
-        <v>6320913</v>
+        <v>6320880</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6652,6 +6640,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6678,10 +6671,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841878</v>
+        <v>122852003</v>
       </c>
       <c r="B53" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6690,41 +6683,53 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584427</v>
+        <v>584646</v>
       </c>
       <c r="R53" t="n">
-        <v>6320982</v>
+        <v>6320922</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6751,9 +6756,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6768,22 +6783,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851640</v>
+        <v>122851735</v>
       </c>
       <c r="B54" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6792,30 +6807,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6828,10 +6843,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584396</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320930</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6901,10 +6916,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851575</v>
+        <v>122840605</v>
       </c>
       <c r="B55" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6934,28 +6949,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R55" t="n">
-        <v>6320915</v>
+        <v>6320873</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6982,50 +6989,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841582</v>
+        <v>122851783</v>
       </c>
       <c r="B56" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7034,55 +7030,53 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584345</v>
+        <v>584336</v>
       </c>
       <c r="R56" t="n">
-        <v>6320948</v>
+        <v>6320920</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7109,9 +7103,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7126,22 +7130,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122840279</v>
+        <v>122851479</v>
       </c>
       <c r="B57" t="n">
-        <v>105461</v>
+        <v>58156</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7154,41 +7158,49 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R57" t="n">
-        <v>6320836</v>
+        <v>6320910</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7215,9 +7227,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7232,22 +7254,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122852003</v>
+        <v>122841912</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7256,53 +7278,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584646</v>
+        <v>584384</v>
       </c>
       <c r="R58" t="n">
-        <v>6320922</v>
+        <v>6320970</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7329,19 +7353,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7356,22 +7370,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851811</v>
+        <v>122841409</v>
       </c>
       <c r="B59" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7380,46 +7394,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584350</v>
+        <v>584384</v>
       </c>
       <c r="R59" t="n">
-        <v>6320916</v>
+        <v>6320921</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7449,50 +7460,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851562</v>
+        <v>122851540</v>
       </c>
       <c r="B60" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7501,30 +7501,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584415</v>
+        <v>584425</v>
       </c>
       <c r="R60" t="n">
-        <v>6320915</v>
+        <v>6320900</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2770,10 +2770,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841596</v>
+        <v>122851756</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2782,41 +2782,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584389</v>
+        <v>584359</v>
       </c>
       <c r="R19" t="n">
-        <v>6320931</v>
+        <v>6320919</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2843,14 +2851,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,28 +2872,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851756</v>
+        <v>122841596</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2889,49 +2903,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584359</v>
+        <v>584389</v>
       </c>
       <c r="R20" t="n">
-        <v>6320919</v>
+        <v>6320931</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2958,19 +2964,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2979,19 +2980,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851562</v>
+        <v>122841518</v>
       </c>
       <c r="B25" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3466,49 +3466,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584415</v>
+        <v>584376</v>
       </c>
       <c r="R25" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3535,50 +3541,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841518</v>
+        <v>122851562</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3587,55 +3582,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R26" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3662,29 +3651,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841855</v>
+        <v>122851724</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4411,20 +4411,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R33" t="n">
-        <v>6320986</v>
+        <v>6320924</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4451,36 +4459,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851724</v>
+        <v>122851662</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4515,7 +4534,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4528,10 +4547,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584375</v>
+        <v>584391</v>
       </c>
       <c r="R34" t="n">
-        <v>6320924</v>
+        <v>6320923</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4601,7 +4620,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851662</v>
+        <v>122851829</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4636,7 +4655,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4649,10 +4668,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584391</v>
+        <v>584348</v>
       </c>
       <c r="R35" t="n">
-        <v>6320923</v>
+        <v>6320915</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4722,7 +4741,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851829</v>
+        <v>122841855</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4755,28 +4774,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R36" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4803,40 +4814,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851811</v>
+        <v>122841088</v>
       </c>
       <c r="B39" t="n">
         <v>98357</v>
@@ -5104,26 +5104,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584350</v>
+        <v>584332</v>
       </c>
       <c r="R39" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5150,47 +5156,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851927</v>
+        <v>122851811</v>
       </c>
       <c r="B40" t="n">
         <v>98357</v>
@@ -5225,7 +5220,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584411</v>
+        <v>584350</v>
       </c>
       <c r="R40" t="n">
-        <v>6320904</v>
+        <v>6320916</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5311,7 +5306,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841088</v>
+        <v>122851927</v>
       </c>
       <c r="B41" t="n">
         <v>98357</v>
@@ -5346,32 +5341,26 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584332</v>
+        <v>584411</v>
       </c>
       <c r="R41" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5398,39 +5387,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841878</v>
+        <v>122852007</v>
       </c>
       <c r="B42" t="n">
-        <v>105463</v>
+        <v>57484</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,41 +5439,53 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584427</v>
+        <v>584646</v>
       </c>
       <c r="R42" t="n">
-        <v>6320982</v>
+        <v>6320922</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5500,9 +5512,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5517,22 +5539,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122852007</v>
+        <v>122841878</v>
       </c>
       <c r="B43" t="n">
-        <v>57484</v>
+        <v>105463</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5541,53 +5563,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584646</v>
+        <v>584427</v>
       </c>
       <c r="R43" t="n">
-        <v>6320922</v>
+        <v>6320982</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5614,19 +5624,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5641,12 +5641,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122839920</v>
+        <v>122852003</v>
       </c>
       <c r="B52" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6576,41 +6576,53 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584525</v>
+        <v>584646</v>
       </c>
       <c r="R52" t="n">
-        <v>6320880</v>
+        <v>6320922</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6637,14 +6649,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6659,22 +6676,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122852003</v>
+        <v>122839920</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6683,53 +6700,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584646</v>
+        <v>584525</v>
       </c>
       <c r="R53" t="n">
-        <v>6320922</v>
+        <v>6320880</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6756,19 +6761,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6783,19 +6783,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851735</v>
+        <v>122840605</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6828,28 +6828,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6876,47 +6868,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122840605</v>
+        <v>122851735</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6949,20 +6930,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R55" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6989,29 +6978,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -3797,10 +3797,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840491</v>
+        <v>122841582</v>
       </c>
       <c r="B28" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3809,41 +3809,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584478</v>
+        <v>584345</v>
       </c>
       <c r="R28" t="n">
-        <v>6320912</v>
+        <v>6320948</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3899,10 +3913,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851862</v>
+        <v>122840491</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3911,49 +3925,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584360</v>
+        <v>584478</v>
       </c>
       <c r="R29" t="n">
-        <v>6320915</v>
+        <v>6320912</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3980,47 +3986,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851590</v>
+        <v>122851862</v>
       </c>
       <c r="B30" t="n">
         <v>98357</v>
@@ -4055,7 +4050,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4068,10 +4063,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584409</v>
+        <v>584360</v>
       </c>
       <c r="R30" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4141,7 +4136,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851716</v>
+        <v>122851590</v>
       </c>
       <c r="B31" t="n">
         <v>98357</v>
@@ -4176,7 +4171,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4189,10 +4184,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584419</v>
+        <v>584409</v>
       </c>
       <c r="R31" t="n">
-        <v>6320935</v>
+        <v>6320920</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4262,7 +4257,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841582</v>
+        <v>122851716</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -4297,32 +4292,26 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584345</v>
+        <v>584419</v>
       </c>
       <c r="R32" t="n">
-        <v>6320948</v>
+        <v>6320935</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4349,36 +4338,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851724</v>
+        <v>122841855</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4411,28 +4411,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584375</v>
+        <v>584419</v>
       </c>
       <c r="R33" t="n">
-        <v>6320924</v>
+        <v>6320986</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4459,47 +4451,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851662</v>
+        <v>122851724</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4534,7 +4515,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4547,10 +4528,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584391</v>
+        <v>584375</v>
       </c>
       <c r="R34" t="n">
-        <v>6320923</v>
+        <v>6320924</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4620,7 +4601,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851829</v>
+        <v>122851662</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4655,7 +4636,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4668,10 +4649,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584348</v>
+        <v>584391</v>
       </c>
       <c r="R35" t="n">
-        <v>6320915</v>
+        <v>6320923</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4741,7 +4722,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841855</v>
+        <v>122851829</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4774,20 +4755,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584419</v>
+        <v>584348</v>
       </c>
       <c r="R36" t="n">
-        <v>6320986</v>
+        <v>6320915</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4814,29 +4803,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841088</v>
+        <v>122851811</v>
       </c>
       <c r="B39" t="n">
         <v>98357</v>
@@ -5104,32 +5104,26 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584332</v>
+        <v>584350</v>
       </c>
       <c r="R39" t="n">
-        <v>6320935</v>
+        <v>6320916</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5156,36 +5150,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851811</v>
+        <v>122851927</v>
       </c>
       <c r="B40" t="n">
         <v>98357</v>
@@ -5220,7 +5225,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5233,10 +5238,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584350</v>
+        <v>584411</v>
       </c>
       <c r="R40" t="n">
-        <v>6320916</v>
+        <v>6320904</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5306,7 +5311,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851927</v>
+        <v>122841088</v>
       </c>
       <c r="B41" t="n">
         <v>98357</v>
@@ -5341,26 +5346,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584411</v>
+        <v>584332</v>
       </c>
       <c r="R41" t="n">
-        <v>6320904</v>
+        <v>6320935</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5387,50 +5398,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122852007</v>
+        <v>122841878</v>
       </c>
       <c r="B42" t="n">
-        <v>57484</v>
+        <v>105463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,53 +5439,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584646</v>
+        <v>584427</v>
       </c>
       <c r="R42" t="n">
-        <v>6320922</v>
+        <v>6320982</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5512,19 +5500,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5539,22 +5517,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122841878</v>
+        <v>122852007</v>
       </c>
       <c r="B43" t="n">
-        <v>105463</v>
+        <v>57484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5563,41 +5541,53 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584427</v>
+        <v>584646</v>
       </c>
       <c r="R43" t="n">
-        <v>6320982</v>
+        <v>6320922</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5624,9 +5614,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5641,12 +5641,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122852003</v>
+        <v>122839920</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6576,53 +6576,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584646</v>
+        <v>584525</v>
       </c>
       <c r="R52" t="n">
-        <v>6320922</v>
+        <v>6320880</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6649,19 +6637,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6676,22 +6659,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122839920</v>
+        <v>122852003</v>
       </c>
       <c r="B53" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6700,41 +6683,53 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584525</v>
+        <v>584646</v>
       </c>
       <c r="R53" t="n">
-        <v>6320880</v>
+        <v>6320922</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6761,14 +6756,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6783,19 +6783,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122840605</v>
+        <v>122851735</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6828,20 +6828,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6868,36 +6876,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851735</v>
+        <v>122840605</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6930,28 +6949,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R55" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6978,40 +6989,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -4378,7 +4378,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841855</v>
+        <v>122851724</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4411,20 +4411,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R33" t="n">
-        <v>6320986</v>
+        <v>6320924</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4451,36 +4459,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851724</v>
+        <v>122851662</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4515,7 +4534,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4528,10 +4547,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584375</v>
+        <v>584391</v>
       </c>
       <c r="R34" t="n">
-        <v>6320924</v>
+        <v>6320923</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4601,7 +4620,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851662</v>
+        <v>122851829</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4636,7 +4655,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4649,10 +4668,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584391</v>
+        <v>584348</v>
       </c>
       <c r="R35" t="n">
-        <v>6320923</v>
+        <v>6320915</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4722,7 +4741,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851829</v>
+        <v>122841855</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4755,28 +4774,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R36" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4803,40 +4814,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851811</v>
+        <v>122841088</v>
       </c>
       <c r="B39" t="n">
         <v>98357</v>
@@ -5104,26 +5104,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584350</v>
+        <v>584332</v>
       </c>
       <c r="R39" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5150,47 +5156,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851927</v>
+        <v>122851811</v>
       </c>
       <c r="B40" t="n">
         <v>98357</v>
@@ -5225,7 +5220,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5238,10 +5233,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584411</v>
+        <v>584350</v>
       </c>
       <c r="R40" t="n">
-        <v>6320904</v>
+        <v>6320916</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5311,7 +5306,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841088</v>
+        <v>122851927</v>
       </c>
       <c r="B41" t="n">
         <v>98357</v>
@@ -5346,32 +5341,26 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584332</v>
+        <v>584411</v>
       </c>
       <c r="R41" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5398,29 +5387,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6564,10 +6564,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122839920</v>
+        <v>122852003</v>
       </c>
       <c r="B52" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6576,41 +6576,53 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584525</v>
+        <v>584646</v>
       </c>
       <c r="R52" t="n">
-        <v>6320880</v>
+        <v>6320922</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6637,14 +6649,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6659,22 +6676,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122852003</v>
+        <v>122839920</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6683,53 +6700,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584646</v>
+        <v>584525</v>
       </c>
       <c r="R53" t="n">
-        <v>6320922</v>
+        <v>6320880</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6756,19 +6761,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6783,19 +6783,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851735</v>
+        <v>122840605</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6828,28 +6828,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6876,47 +6868,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122840605</v>
+        <v>122851735</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6949,20 +6930,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R55" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6989,29 +6978,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,7 +2440,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851599</v>
+        <v>122841088</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2475,26 +2475,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584395</v>
+        <v>584332</v>
       </c>
       <c r="R16" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2521,47 +2527,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841533</v>
+        <v>122851623</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2594,20 +2589,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584369</v>
+        <v>584406</v>
       </c>
       <c r="R17" t="n">
-        <v>6320926</v>
+        <v>6320924</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2634,14 +2637,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2650,25 +2658,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122842080</v>
+        <v>122851862</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2701,20 +2710,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584434</v>
+        <v>584360</v>
       </c>
       <c r="R18" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2741,39 +2758,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851756</v>
+        <v>122851605</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2782,30 +2810,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2818,10 +2846,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584359</v>
+        <v>584395</v>
       </c>
       <c r="R19" t="n">
-        <v>6320919</v>
+        <v>6320916</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2891,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841596</v>
+        <v>122851590</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2903,41 +2931,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584389</v>
+        <v>584409</v>
       </c>
       <c r="R20" t="n">
-        <v>6320931</v>
+        <v>6320920</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2964,14 +3000,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2980,25 +3021,26 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841328</v>
+        <v>122841518</v>
       </c>
       <c r="B21" t="n">
         <v>98357</v>
@@ -3031,20 +3073,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584336</v>
+        <v>584376</v>
       </c>
       <c r="R21" t="n">
-        <v>6320932</v>
+        <v>6320937</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3074,11 +3130,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,22 +3144,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841069</v>
+        <v>122839920</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3117,25 +3168,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3145,10 +3196,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584349</v>
+        <v>584525</v>
       </c>
       <c r="R22" t="n">
-        <v>6320925</v>
+        <v>6320880</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3185,7 +3236,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>50-tal plantor</t>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3212,7 +3263,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851575</v>
+        <v>122851662</v>
       </c>
       <c r="B23" t="n">
         <v>98357</v>
@@ -3247,7 +3298,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3260,10 +3311,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584415</v>
+        <v>584391</v>
       </c>
       <c r="R23" t="n">
-        <v>6320915</v>
+        <v>6320923</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3333,7 +3384,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851469</v>
+        <v>122851724</v>
       </c>
       <c r="B24" t="n">
         <v>98357</v>
@@ -3368,7 +3419,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3381,10 +3432,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584584</v>
+        <v>584375</v>
       </c>
       <c r="R24" t="n">
-        <v>6320910</v>
+        <v>6320924</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3454,7 +3505,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841518</v>
+        <v>122851575</v>
       </c>
       <c r="B25" t="n">
         <v>98357</v>
@@ -3489,32 +3540,26 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R25" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3541,39 +3586,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851562</v>
+        <v>122839339</v>
       </c>
       <c r="B26" t="n">
-        <v>105463</v>
+        <v>95128</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,45 +3642,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584415</v>
+        <v>584548</v>
       </c>
       <c r="R26" t="n">
-        <v>6320915</v>
+        <v>6320905</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3651,47 +3699,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840279</v>
+        <v>122851640</v>
       </c>
       <c r="B27" t="n">
         <v>105463</v>
@@ -3726,22 +3763,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584419</v>
+        <v>584396</v>
       </c>
       <c r="R27" t="n">
-        <v>6320836</v>
+        <v>6320930</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3768,36 +3809,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841582</v>
+        <v>122840605</v>
       </c>
       <c r="B28" t="n">
         <v>98357</v>
@@ -3830,34 +3882,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584345</v>
+        <v>584384</v>
       </c>
       <c r="R28" t="n">
-        <v>6320948</v>
+        <v>6320873</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3901,12 +3939,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4015,10 +4053,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851862</v>
+        <v>122841878</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4027,49 +4065,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584360</v>
+        <v>584427</v>
       </c>
       <c r="R30" t="n">
-        <v>6320915</v>
+        <v>6320982</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4096,47 +4126,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851590</v>
+        <v>122839190</v>
       </c>
       <c r="B31" t="n">
         <v>98357</v>
@@ -4169,28 +4188,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584409</v>
+        <v>584581</v>
       </c>
       <c r="R31" t="n">
-        <v>6320920</v>
+        <v>6320913</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4217,47 +4228,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851716</v>
+        <v>122841855</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -4290,28 +4290,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>584419</v>
       </c>
       <c r="R32" t="n">
-        <v>6320935</v>
+        <v>6320986</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4338,50 +4330,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851724</v>
+        <v>122852007</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>57484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4390,35 +4371,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4426,10 +4411,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584375</v>
+        <v>584646</v>
       </c>
       <c r="R33" t="n">
-        <v>6320924</v>
+        <v>6320922</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4480,7 +4465,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4499,10 +4483,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851662</v>
+        <v>122851479</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>58156</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,25 +4495,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4537,9 +4521,13 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4547,10 +4535,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584391</v>
+        <v>584584</v>
       </c>
       <c r="R34" t="n">
-        <v>6320923</v>
+        <v>6320910</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4601,7 +4589,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4620,7 +4607,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851829</v>
+        <v>122851540</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4655,7 +4642,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4668,10 +4655,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584348</v>
+        <v>584425</v>
       </c>
       <c r="R35" t="n">
-        <v>6320915</v>
+        <v>6320900</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4741,7 +4728,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841855</v>
+        <v>122842080</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4781,13 +4768,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584419</v>
+        <v>584434</v>
       </c>
       <c r="R36" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4843,10 +4830,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851741</v>
+        <v>122841409</v>
       </c>
       <c r="B37" t="n">
-        <v>57848</v>
+        <v>57369</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4855,20 +4842,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4876,29 +4863,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R37" t="n">
-        <v>6320937</v>
+        <v>6320921</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4928,19 +4908,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4955,12 +4925,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5069,10 +5039,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841088</v>
+        <v>122852003</v>
       </c>
       <c r="B39" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5081,55 +5051,53 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584332</v>
+        <v>584646</v>
       </c>
       <c r="R39" t="n">
-        <v>6320935</v>
+        <v>6320922</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5156,9 +5124,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5173,22 +5151,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851811</v>
+        <v>122851504</v>
       </c>
       <c r="B40" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5197,32 +5175,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -5233,10 +5207,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584350</v>
+        <v>584532</v>
       </c>
       <c r="R40" t="n">
-        <v>6320916</v>
+        <v>6320881</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5306,7 +5280,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851927</v>
+        <v>122851869</v>
       </c>
       <c r="B41" t="n">
         <v>98357</v>
@@ -5341,7 +5315,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5354,7 +5328,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584411</v>
+        <v>584369</v>
       </c>
       <c r="R41" t="n">
         <v>6320904</v>
@@ -5427,10 +5401,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841878</v>
+        <v>122841328</v>
       </c>
       <c r="B42" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,41 +5413,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584427</v>
+        <v>584336</v>
       </c>
       <c r="R42" t="n">
-        <v>6320982</v>
+        <v>6320932</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5503,6 +5477,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5529,10 +5508,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122852007</v>
+        <v>122851811</v>
       </c>
       <c r="B43" t="n">
-        <v>57484</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5541,39 +5520,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5581,10 +5556,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584646</v>
+        <v>584350</v>
       </c>
       <c r="R43" t="n">
-        <v>6320922</v>
+        <v>6320916</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5635,6 +5610,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5653,10 +5629,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851504</v>
+        <v>122841069</v>
       </c>
       <c r="B44" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5665,45 +5641,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584532</v>
+        <v>584349</v>
       </c>
       <c r="R44" t="n">
-        <v>6320881</v>
+        <v>6320925</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5730,19 +5702,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5751,26 +5718,25 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851640</v>
+        <v>122851562</v>
       </c>
       <c r="B45" t="n">
         <v>105463</v>
@@ -5805,7 +5771,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5818,10 +5784,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584396</v>
+        <v>584415</v>
       </c>
       <c r="R45" t="n">
-        <v>6320930</v>
+        <v>6320915</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5891,7 +5857,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851623</v>
+        <v>122851756</v>
       </c>
       <c r="B46" t="n">
         <v>98357</v>
@@ -5926,7 +5892,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5939,10 +5905,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584406</v>
+        <v>584359</v>
       </c>
       <c r="R46" t="n">
-        <v>6320924</v>
+        <v>6320919</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6012,7 +5978,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122839190</v>
+        <v>122851735</v>
       </c>
       <c r="B47" t="n">
         <v>98357</v>
@@ -6045,20 +6011,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584581</v>
+        <v>584357</v>
       </c>
       <c r="R47" t="n">
-        <v>6320913</v>
+        <v>6320937</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6085,39 +6059,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122839339</v>
+        <v>122851716</v>
       </c>
       <c r="B48" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6126,41 +6111,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584548</v>
+        <v>584419</v>
       </c>
       <c r="R48" t="n">
-        <v>6320905</v>
+        <v>6320935</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6187,39 +6180,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841954</v>
+        <v>122851783</v>
       </c>
       <c r="B49" t="n">
-        <v>90964</v>
+        <v>57369</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6232,21 +6236,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>100001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6254,19 +6258,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584450</v>
+        <v>584336</v>
       </c>
       <c r="R49" t="n">
-        <v>6321001</v>
+        <v>6320920</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6293,9 +6305,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6310,22 +6332,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851869</v>
+        <v>122851741</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6334,35 +6356,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6370,10 +6396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584369</v>
+        <v>584357</v>
       </c>
       <c r="R50" t="n">
-        <v>6320904</v>
+        <v>6320937</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6424,7 +6450,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6443,10 +6468,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851605</v>
+        <v>122841582</v>
       </c>
       <c r="B51" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6455,49 +6480,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584395</v>
+        <v>584345</v>
       </c>
       <c r="R51" t="n">
-        <v>6320916</v>
+        <v>6320948</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6524,50 +6555,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122852003</v>
+        <v>122841954</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6580,21 +6600,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6602,27 +6622,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584646</v>
+        <v>584450</v>
       </c>
       <c r="R52" t="n">
-        <v>6320922</v>
+        <v>6321001</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6649,19 +6661,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6676,22 +6678,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122839920</v>
+        <v>122841533</v>
       </c>
       <c r="B53" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6700,25 +6702,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6728,10 +6730,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320880</v>
+        <v>6320926</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6768,7 +6770,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6795,7 +6797,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122840605</v>
+        <v>122841912</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6828,20 +6830,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>584384</v>
       </c>
       <c r="R54" t="n">
-        <v>6320873</v>
+        <v>6320970</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6885,19 +6901,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851735</v>
+        <v>122851829</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6932,7 +6948,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6945,10 +6961,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584357</v>
+        <v>584348</v>
       </c>
       <c r="R55" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7018,10 +7034,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851783</v>
+        <v>122841596</v>
       </c>
       <c r="B56" t="n">
-        <v>57369</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7034,16 +7050,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7051,32 +7067,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584336</v>
+        <v>584389</v>
       </c>
       <c r="R56" t="n">
-        <v>6320920</v>
+        <v>6320931</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7103,19 +7107,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7130,22 +7129,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851479</v>
+        <v>122851469</v>
       </c>
       <c r="B57" t="n">
-        <v>58156</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7154,39 +7153,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7248,6 +7243,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7266,10 +7262,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841912</v>
+        <v>122840279</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7278,55 +7274,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320970</v>
+        <v>6320836</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7370,22 +7356,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841409</v>
+        <v>122851599</v>
       </c>
       <c r="B59" t="n">
-        <v>57369</v>
+        <v>98357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7394,43 +7380,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584384</v>
+        <v>584395</v>
       </c>
       <c r="R59" t="n">
-        <v>6320921</v>
+        <v>6320916</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7460,36 +7449,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851540</v>
+        <v>122851927</v>
       </c>
       <c r="B60" t="n">
         <v>98357</v>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584425</v>
+        <v>584411</v>
       </c>
       <c r="R60" t="n">
-        <v>6320900</v>
+        <v>6320904</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -5163,10 +5163,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851504</v>
+        <v>122841328</v>
       </c>
       <c r="B40" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5175,45 +5175,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584532</v>
+        <v>584336</v>
       </c>
       <c r="R40" t="n">
-        <v>6320881</v>
+        <v>6320932</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5240,19 +5236,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5261,19 +5252,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5401,10 +5391,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841328</v>
+        <v>122851504</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5413,41 +5403,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584336</v>
+        <v>584532</v>
       </c>
       <c r="R42" t="n">
-        <v>6320932</v>
+        <v>6320881</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5474,14 +5468,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5490,18 +5489,19 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851756</v>
+        <v>122851735</v>
       </c>
       <c r="B46" t="n">
         <v>98357</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5905,10 +5905,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584359</v>
+        <v>584357</v>
       </c>
       <c r="R46" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5978,7 +5978,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851735</v>
+        <v>122851716</v>
       </c>
       <c r="B47" t="n">
         <v>98357</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R47" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6099,7 +6099,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851716</v>
+        <v>122851756</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584419</v>
+        <v>584359</v>
       </c>
       <c r="R48" t="n">
-        <v>6320935</v>
+        <v>6320919</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841954</v>
+        <v>122841533</v>
       </c>
       <c r="B52" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6596,45 +6596,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584450</v>
+        <v>584369</v>
       </c>
       <c r="R52" t="n">
-        <v>6321001</v>
+        <v>6320926</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6664,6 +6660,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6678,19 +6679,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841533</v>
+        <v>122841912</v>
       </c>
       <c r="B53" t="n">
         <v>98357</v>
@@ -6723,20 +6724,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584384</v>
       </c>
       <c r="R53" t="n">
-        <v>6320926</v>
+        <v>6320970</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6766,11 +6781,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6785,19 +6795,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122841912</v>
+        <v>122851829</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6832,32 +6842,26 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584384</v>
+        <v>584348</v>
       </c>
       <c r="R54" t="n">
-        <v>6320970</v>
+        <v>6320915</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6884,39 +6888,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851829</v>
+        <v>122841954</v>
       </c>
       <c r="B55" t="n">
-        <v>98357</v>
+        <v>90964</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6925,49 +6940,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584348</v>
+        <v>584450</v>
       </c>
       <c r="R55" t="n">
-        <v>6320915</v>
+        <v>6321001</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6994,50 +7005,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841596</v>
+        <v>122840279</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7046,38 +7046,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584389</v>
+        <v>584419</v>
       </c>
       <c r="R56" t="n">
-        <v>6320931</v>
+        <v>6320836</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7110,11 +7114,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7141,10 +7140,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851469</v>
+        <v>122841596</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7153,49 +7152,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584584</v>
+        <v>584389</v>
       </c>
       <c r="R57" t="n">
-        <v>6320910</v>
+        <v>6320931</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7222,19 +7213,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7243,29 +7229,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840279</v>
+        <v>122851469</v>
       </c>
       <c r="B58" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7274,45 +7259,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R58" t="n">
-        <v>6320836</v>
+        <v>6320910</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7339,29 +7328,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -3626,10 +3626,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122839339</v>
+        <v>122840605</v>
       </c>
       <c r="B26" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3638,41 +3638,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584548</v>
+        <v>584384</v>
       </c>
       <c r="R26" t="n">
-        <v>6320905</v>
+        <v>6320873</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3716,12 +3716,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840605</v>
+        <v>122839339</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3861,41 +3861,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584384</v>
+        <v>584548</v>
       </c>
       <c r="R28" t="n">
-        <v>6320873</v>
+        <v>6320905</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3939,22 +3939,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840491</v>
+        <v>122839190</v>
       </c>
       <c r="B29" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3963,41 +3963,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584478</v>
+        <v>584581</v>
       </c>
       <c r="R29" t="n">
-        <v>6320912</v>
+        <v>6320913</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4041,22 +4041,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841878</v>
+        <v>122841855</v>
       </c>
       <c r="B30" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4065,25 +4065,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584427</v>
+        <v>584419</v>
       </c>
       <c r="R30" t="n">
-        <v>6320982</v>
+        <v>6320986</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4155,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122839190</v>
+        <v>122840491</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4167,41 +4167,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584581</v>
+        <v>584478</v>
       </c>
       <c r="R31" t="n">
-        <v>6320913</v>
+        <v>6320912</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4245,22 +4245,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841855</v>
+        <v>122841878</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4269,25 +4269,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584419</v>
+        <v>584427</v>
       </c>
       <c r="R32" t="n">
-        <v>6320986</v>
+        <v>6320982</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122852007</v>
+        <v>122842080</v>
       </c>
       <c r="B33" t="n">
-        <v>57484</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4371,53 +4371,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584646</v>
+        <v>584434</v>
       </c>
       <c r="R33" t="n">
-        <v>6320922</v>
+        <v>6320937</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4444,19 +4432,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4471,12 +4449,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4728,10 +4706,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842080</v>
+        <v>122852007</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>57484</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4740,41 +4718,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584434</v>
+        <v>584646</v>
       </c>
       <c r="R36" t="n">
-        <v>6320937</v>
+        <v>6320922</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4801,9 +4791,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4818,12 +4818,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841328</v>
+        <v>122851504</v>
       </c>
       <c r="B40" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5175,41 +5175,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584336</v>
+        <v>584532</v>
       </c>
       <c r="R40" t="n">
-        <v>6320932</v>
+        <v>6320881</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5236,14 +5240,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5252,18 +5261,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5391,10 +5401,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851504</v>
+        <v>122841328</v>
       </c>
       <c r="B42" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5403,45 +5413,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584532</v>
+        <v>584336</v>
       </c>
       <c r="R42" t="n">
-        <v>6320881</v>
+        <v>6320932</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5468,19 +5474,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5489,19 +5490,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851735</v>
+        <v>122851756</v>
       </c>
       <c r="B46" t="n">
         <v>98357</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5905,10 +5905,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584357</v>
+        <v>584359</v>
       </c>
       <c r="R46" t="n">
-        <v>6320937</v>
+        <v>6320919</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5978,7 +5978,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851716</v>
+        <v>122851735</v>
       </c>
       <c r="B47" t="n">
         <v>98357</v>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6026,10 +6026,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584419</v>
+        <v>584357</v>
       </c>
       <c r="R47" t="n">
-        <v>6320935</v>
+        <v>6320937</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6099,7 +6099,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851756</v>
+        <v>122851716</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584359</v>
+        <v>584419</v>
       </c>
       <c r="R48" t="n">
-        <v>6320919</v>
+        <v>6320935</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851783</v>
+        <v>122851741</v>
       </c>
       <c r="B49" t="n">
-        <v>57369</v>
+        <v>57848</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6232,20 +6232,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100001</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584336</v>
+        <v>584357</v>
       </c>
       <c r="R49" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851741</v>
+        <v>122851783</v>
       </c>
       <c r="B50" t="n">
-        <v>57848</v>
+        <v>57369</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6356,20 +6356,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6379,14 +6379,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584357</v>
+        <v>584336</v>
       </c>
       <c r="R50" t="n">
-        <v>6320937</v>
+        <v>6320920</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122840279</v>
+        <v>122841596</v>
       </c>
       <c r="B56" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7046,42 +7046,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584419</v>
+        <v>584389</v>
       </c>
       <c r="R56" t="n">
-        <v>6320836</v>
+        <v>6320931</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7114,6 +7110,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7140,10 +7141,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841596</v>
+        <v>122851469</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7152,41 +7153,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R57" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7213,14 +7222,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7229,28 +7243,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851469</v>
+        <v>122840279</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,49 +7274,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320910</v>
+        <v>6320836</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7328,40 +7339,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122841088</v>
+        <v>122851927</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2475,32 +2475,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584332</v>
+        <v>584411</v>
       </c>
       <c r="R16" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2527,39 +2521,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851623</v>
+        <v>122841518</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2591,26 +2596,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584406</v>
+        <v>584376</v>
       </c>
       <c r="R17" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2637,50 +2648,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851862</v>
+        <v>122841409</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>57369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2689,46 +2689,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584360</v>
+        <v>584384</v>
       </c>
       <c r="R18" t="n">
-        <v>6320915</v>
+        <v>6320921</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2758,50 +2755,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851605</v>
+        <v>122851716</v>
       </c>
       <c r="B19" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2810,30 +2796,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2846,10 +2832,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584395</v>
+        <v>584419</v>
       </c>
       <c r="R19" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2919,10 +2905,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851590</v>
+        <v>122851869</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2954,7 +2940,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2967,10 +2953,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584409</v>
+        <v>584369</v>
       </c>
       <c r="R20" t="n">
-        <v>6320920</v>
+        <v>6320904</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3040,10 +3026,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841518</v>
+        <v>122851575</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3075,32 +3061,26 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R21" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3127,39 +3107,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122839920</v>
+        <v>122851811</v>
       </c>
       <c r="B22" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3168,41 +3159,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584525</v>
+        <v>584350</v>
       </c>
       <c r="R22" t="n">
-        <v>6320880</v>
+        <v>6320916</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3229,14 +3228,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3245,28 +3249,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851662</v>
+        <v>122840797</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3296,28 +3301,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584391</v>
+        <v>584406</v>
       </c>
       <c r="R23" t="n">
-        <v>6320923</v>
+        <v>6320860</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3344,50 +3341,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851724</v>
+        <v>122840491</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3396,49 +3382,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584375</v>
+        <v>584478</v>
       </c>
       <c r="R24" t="n">
-        <v>6320924</v>
+        <v>6320912</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3465,50 +3443,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851575</v>
+        <v>122852003</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3517,35 +3484,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3553,10 +3524,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584415</v>
+        <v>584646</v>
       </c>
       <c r="R25" t="n">
-        <v>6320915</v>
+        <v>6320922</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3607,7 +3578,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3629,7 +3599,7 @@
         <v>122840605</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3731,7 +3701,7 @@
         <v>122851640</v>
       </c>
       <c r="B27" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3849,10 +3819,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122839339</v>
+        <v>122851741</v>
       </c>
       <c r="B28" t="n">
-        <v>95128</v>
+        <v>57848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3865,37 +3835,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584548</v>
+        <v>584357</v>
       </c>
       <c r="R28" t="n">
-        <v>6320905</v>
+        <v>6320937</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3922,9 +3904,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3939,22 +3931,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122839190</v>
+        <v>122851599</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3984,20 +3976,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584581</v>
+        <v>584395</v>
       </c>
       <c r="R29" t="n">
-        <v>6320913</v>
+        <v>6320916</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4024,39 +4024,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841855</v>
+        <v>122851829</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,20 +4097,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584419</v>
+        <v>584348</v>
       </c>
       <c r="R30" t="n">
-        <v>6320986</v>
+        <v>6320915</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4126,39 +4145,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840491</v>
+        <v>122839339</v>
       </c>
       <c r="B31" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4191,17 +4221,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584478</v>
+        <v>584548</v>
       </c>
       <c r="R31" t="n">
-        <v>6320912</v>
+        <v>6320905</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4257,10 +4287,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841878</v>
+        <v>122841088</v>
       </c>
       <c r="B32" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4269,41 +4299,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584427</v>
+        <v>584332</v>
       </c>
       <c r="R32" t="n">
-        <v>6320982</v>
+        <v>6320935</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4347,22 +4391,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842080</v>
+        <v>122841582</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4392,20 +4436,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584434</v>
+        <v>584345</v>
       </c>
       <c r="R33" t="n">
-        <v>6320937</v>
+        <v>6320948</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4449,22 +4507,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851479</v>
+        <v>122852007</v>
       </c>
       <c r="B34" t="n">
-        <v>58156</v>
+        <v>57484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4473,20 +4531,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4496,14 +4554,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4513,10 +4571,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584584</v>
+        <v>584646</v>
       </c>
       <c r="R34" t="n">
-        <v>6320910</v>
+        <v>6320922</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4585,10 +4643,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851540</v>
+        <v>122841954</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>90972</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4597,49 +4655,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584425</v>
+        <v>584450</v>
       </c>
       <c r="R35" t="n">
-        <v>6320900</v>
+        <v>6321001</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4666,50 +4720,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122852007</v>
+        <v>122851479</v>
       </c>
       <c r="B36" t="n">
-        <v>57484</v>
+        <v>58156</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4718,20 +4761,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100048</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4741,14 +4784,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4758,10 +4801,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584646</v>
+        <v>584584</v>
       </c>
       <c r="R36" t="n">
-        <v>6320922</v>
+        <v>6320910</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4830,10 +4873,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841409</v>
+        <v>122839920</v>
       </c>
       <c r="B37" t="n">
-        <v>57369</v>
+        <v>95136</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4842,46 +4885,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100001</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584384</v>
+        <v>584525</v>
       </c>
       <c r="R37" t="n">
-        <v>6320921</v>
+        <v>6320880</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4911,6 +4949,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4937,10 +4980,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122840797</v>
+        <v>122851504</v>
       </c>
       <c r="B38" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4949,41 +4992,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584406</v>
+        <v>584532</v>
       </c>
       <c r="R38" t="n">
-        <v>6320860</v>
+        <v>6320881</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5010,39 +5057,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122852003</v>
+        <v>122851735</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5051,39 +5109,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5091,10 +5145,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584646</v>
+        <v>584357</v>
       </c>
       <c r="R39" t="n">
-        <v>6320922</v>
+        <v>6320937</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5145,6 +5199,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5163,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851504</v>
+        <v>122851562</v>
       </c>
       <c r="B40" t="n">
-        <v>95128</v>
+        <v>105471</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5179,24 +5234,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -5207,10 +5266,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584532</v>
+        <v>584415</v>
       </c>
       <c r="R40" t="n">
-        <v>6320881</v>
+        <v>6320915</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5280,10 +5339,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851869</v>
+        <v>122841533</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5313,28 +5372,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>584369</v>
       </c>
       <c r="R41" t="n">
-        <v>6320904</v>
+        <v>6320926</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5361,19 +5412,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5382,29 +5428,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841328</v>
+        <v>122851783</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>57369</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5413,41 +5458,53 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>584336</v>
       </c>
       <c r="R42" t="n">
-        <v>6320932</v>
+        <v>6320920</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5474,14 +5531,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5496,22 +5558,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851811</v>
+        <v>122851623</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5543,7 +5605,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5556,10 +5618,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584350</v>
+        <v>584406</v>
       </c>
       <c r="R43" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5629,10 +5691,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841069</v>
+        <v>122840279</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5641,38 +5703,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584349</v>
+        <v>584419</v>
       </c>
       <c r="R44" t="n">
-        <v>6320925</v>
+        <v>6320836</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5705,11 +5771,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5736,10 +5797,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851562</v>
+        <v>122839190</v>
       </c>
       <c r="B45" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5748,49 +5809,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584415</v>
+        <v>584581</v>
       </c>
       <c r="R45" t="n">
-        <v>6320915</v>
+        <v>6320913</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5817,50 +5870,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851756</v>
+        <v>122841069</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5890,28 +5932,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584359</v>
+        <v>584349</v>
       </c>
       <c r="R46" t="n">
-        <v>6320919</v>
+        <v>6320925</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5938,19 +5972,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5959,29 +5988,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851735</v>
+        <v>122851724</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6013,7 +6041,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6026,10 +6054,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584357</v>
+        <v>584375</v>
       </c>
       <c r="R47" t="n">
-        <v>6320937</v>
+        <v>6320924</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6099,10 +6127,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851716</v>
+        <v>122841328</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6132,28 +6160,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584419</v>
+        <v>584336</v>
       </c>
       <c r="R48" t="n">
-        <v>6320935</v>
+        <v>6320932</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6180,19 +6200,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6201,29 +6216,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851741</v>
+        <v>122841855</v>
       </c>
       <c r="B49" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6232,53 +6246,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R49" t="n">
-        <v>6320937</v>
+        <v>6320986</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6305,19 +6307,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6332,22 +6324,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851783</v>
+        <v>122841596</v>
       </c>
       <c r="B50" t="n">
-        <v>57369</v>
+        <v>57494</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6360,16 +6352,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6377,32 +6369,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584336</v>
+        <v>584389</v>
       </c>
       <c r="R50" t="n">
-        <v>6320920</v>
+        <v>6320931</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6429,19 +6409,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6456,22 +6431,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122841582</v>
+        <v>122851540</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6503,32 +6478,26 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584345</v>
+        <v>584425</v>
       </c>
       <c r="R51" t="n">
-        <v>6320948</v>
+        <v>6320900</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6555,39 +6524,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841533</v>
+        <v>122851756</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6617,20 +6597,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584369</v>
+        <v>584359</v>
       </c>
       <c r="R52" t="n">
-        <v>6320926</v>
+        <v>6320919</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6657,14 +6645,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6673,28 +6666,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841912</v>
+        <v>122851469</v>
       </c>
       <c r="B53" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6726,32 +6720,26 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584384</v>
+        <v>584584</v>
       </c>
       <c r="R53" t="n">
-        <v>6320970</v>
+        <v>6320910</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6778,39 +6766,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851829</v>
+        <v>122851590</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6842,7 +6841,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6855,10 +6854,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584348</v>
+        <v>584409</v>
       </c>
       <c r="R54" t="n">
-        <v>6320915</v>
+        <v>6320920</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6928,10 +6927,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841954</v>
+        <v>122851662</v>
       </c>
       <c r="B55" t="n">
-        <v>90964</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6940,45 +6939,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584450</v>
+        <v>584391</v>
       </c>
       <c r="R55" t="n">
-        <v>6321001</v>
+        <v>6320923</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7005,39 +7008,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841596</v>
+        <v>122851605</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7046,41 +7060,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584389</v>
+        <v>584395</v>
       </c>
       <c r="R56" t="n">
-        <v>6320931</v>
+        <v>6320916</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7107,14 +7129,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7123,28 +7150,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851469</v>
+        <v>122841878</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7153,49 +7181,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584584</v>
+        <v>584427</v>
       </c>
       <c r="R57" t="n">
-        <v>6320910</v>
+        <v>6320982</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7222,50 +7242,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840279</v>
+        <v>122842080</v>
       </c>
       <c r="B58" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7274,45 +7283,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584434</v>
       </c>
       <c r="R58" t="n">
-        <v>6320836</v>
+        <v>6320937</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7368,10 +7373,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851599</v>
+        <v>122841912</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7403,26 +7408,32 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584395</v>
+        <v>584384</v>
       </c>
       <c r="R59" t="n">
-        <v>6320916</v>
+        <v>6320970</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7449,50 +7460,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851927</v>
+        <v>122851862</v>
       </c>
       <c r="B60" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584411</v>
+        <v>584360</v>
       </c>
       <c r="R60" t="n">
-        <v>6320904</v>
+        <v>6320915</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2561,10 +2561,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841518</v>
+        <v>122841409</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,55 +2573,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584376</v>
+        <v>584384</v>
       </c>
       <c r="R17" t="n">
-        <v>6320937</v>
+        <v>6320921</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2665,22 +2656,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841409</v>
+        <v>122841518</v>
       </c>
       <c r="B18" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2689,46 +2680,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584384</v>
+        <v>584376</v>
       </c>
       <c r="R18" t="n">
-        <v>6320921</v>
+        <v>6320937</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2772,12 +2772,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122852003</v>
+        <v>122851640</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3484,39 +3484,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3524,10 +3520,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584646</v>
+        <v>584396</v>
       </c>
       <c r="R25" t="n">
-        <v>6320922</v>
+        <v>6320930</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3578,6 +3574,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3596,10 +3593,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840605</v>
+        <v>122852003</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3608,41 +3605,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584384</v>
+        <v>584646</v>
       </c>
       <c r="R26" t="n">
-        <v>6320873</v>
+        <v>6320922</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3669,9 +3678,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3686,22 +3705,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851640</v>
+        <v>122840605</v>
       </c>
       <c r="B27" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3710,49 +3729,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584396</v>
+        <v>584384</v>
       </c>
       <c r="R27" t="n">
-        <v>6320930</v>
+        <v>6320873</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3779,40 +3790,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122839339</v>
+        <v>122841088</v>
       </c>
       <c r="B31" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4197,41 +4197,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584548</v>
+        <v>584332</v>
       </c>
       <c r="R31" t="n">
-        <v>6320905</v>
+        <v>6320935</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4287,7 +4301,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841088</v>
+        <v>122841582</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4322,7 +4336,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4337,17 +4351,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584332</v>
+        <v>584345</v>
       </c>
       <c r="R32" t="n">
-        <v>6320935</v>
+        <v>6320948</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4403,10 +4417,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841582</v>
+        <v>122839339</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4415,52 +4429,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584345</v>
+        <v>584548</v>
       </c>
       <c r="R33" t="n">
-        <v>6320948</v>
+        <v>6320905</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122839920</v>
+        <v>122841533</v>
       </c>
       <c r="B37" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4885,25 +4885,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R37" t="n">
-        <v>6320880</v>
+        <v>6320926</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851504</v>
+        <v>122851735</v>
       </c>
       <c r="B38" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4992,28 +4992,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -5024,10 +5028,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584532</v>
+        <v>584357</v>
       </c>
       <c r="R38" t="n">
-        <v>6320881</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5097,10 +5101,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851735</v>
+        <v>122851562</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5109,30 +5113,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5145,10 +5149,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584357</v>
+        <v>584415</v>
       </c>
       <c r="R39" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5218,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851562</v>
+        <v>122839920</v>
       </c>
       <c r="B40" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,45 +5238,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584415</v>
+        <v>584525</v>
       </c>
       <c r="R40" t="n">
-        <v>6320915</v>
+        <v>6320880</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5299,19 +5295,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5320,29 +5311,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841533</v>
+        <v>122851504</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5351,41 +5341,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584369</v>
+        <v>584532</v>
       </c>
       <c r="R41" t="n">
-        <v>6320926</v>
+        <v>6320881</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5412,14 +5406,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5428,28 +5427,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851783</v>
+        <v>122851623</v>
       </c>
       <c r="B42" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5458,39 +5458,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5498,10 +5494,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584336</v>
+        <v>584406</v>
       </c>
       <c r="R42" t="n">
-        <v>6320920</v>
+        <v>6320924</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5552,6 +5548,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5570,10 +5567,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851623</v>
+        <v>122851783</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5582,35 +5579,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5618,10 +5619,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584406</v>
+        <v>584336</v>
       </c>
       <c r="R43" t="n">
-        <v>6320924</v>
+        <v>6320920</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5672,7 +5673,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6127,7 +6127,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841328</v>
+        <v>122851540</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6160,20 +6160,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R48" t="n">
-        <v>6320932</v>
+        <v>6320900</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6200,14 +6208,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6216,25 +6229,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841855</v>
+        <v>122851756</v>
       </c>
       <c r="B49" t="n">
         <v>98365</v>
@@ -6267,20 +6281,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584419</v>
+        <v>584359</v>
       </c>
       <c r="R49" t="n">
-        <v>6320986</v>
+        <v>6320919</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6307,39 +6329,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841596</v>
+        <v>122851469</v>
       </c>
       <c r="B50" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6348,41 +6381,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R50" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6409,14 +6450,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6425,25 +6471,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851540</v>
+        <v>122851590</v>
       </c>
       <c r="B51" t="n">
         <v>98365</v>
@@ -6478,7 +6525,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -6491,10 +6538,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584425</v>
+        <v>584409</v>
       </c>
       <c r="R51" t="n">
-        <v>6320900</v>
+        <v>6320920</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6564,7 +6611,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851756</v>
+        <v>122851662</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6599,7 +6646,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -6612,10 +6659,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584359</v>
+        <v>584391</v>
       </c>
       <c r="R52" t="n">
-        <v>6320919</v>
+        <v>6320923</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6685,7 +6732,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851469</v>
+        <v>122841328</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6718,28 +6765,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584584</v>
+        <v>584336</v>
       </c>
       <c r="R53" t="n">
-        <v>6320910</v>
+        <v>6320932</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6766,19 +6805,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6787,26 +6821,25 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851590</v>
+        <v>122841855</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6839,28 +6872,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584409</v>
+        <v>584419</v>
       </c>
       <c r="R54" t="n">
-        <v>6320920</v>
+        <v>6320986</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6887,50 +6912,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851662</v>
+        <v>122851605</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6939,30 +6953,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6975,10 +6989,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584391</v>
+        <v>584395</v>
       </c>
       <c r="R55" t="n">
-        <v>6320923</v>
+        <v>6320916</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7048,10 +7062,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851605</v>
+        <v>122841596</v>
       </c>
       <c r="B56" t="n">
-        <v>105471</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7060,49 +7074,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584395</v>
+        <v>584389</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320931</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7129,19 +7135,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7150,29 +7151,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841878</v>
+        <v>122851862</v>
       </c>
       <c r="B57" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7181,41 +7181,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584427</v>
+        <v>584360</v>
       </c>
       <c r="R57" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7242,39 +7250,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122842080</v>
+        <v>122841878</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7283,25 +7302,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7311,13 +7330,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584434</v>
+        <v>584427</v>
       </c>
       <c r="R58" t="n">
-        <v>6320937</v>
+        <v>6320982</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7373,7 +7392,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841912</v>
+        <v>122842080</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7406,34 +7425,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584384</v>
+        <v>584434</v>
       </c>
       <c r="R59" t="n">
-        <v>6320970</v>
+        <v>6320937</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7477,19 +7482,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851862</v>
+        <v>122841912</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7524,26 +7529,32 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584360</v>
+        <v>584384</v>
       </c>
       <c r="R60" t="n">
-        <v>6320915</v>
+        <v>6320970</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7570,40 +7581,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,7 +2440,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851927</v>
+        <v>122839190</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2473,28 +2473,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584411</v>
+        <v>584581</v>
       </c>
       <c r="R16" t="n">
-        <v>6320904</v>
+        <v>6320913</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2521,50 +2513,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841409</v>
+        <v>122851662</v>
       </c>
       <c r="B17" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,43 +2554,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584384</v>
+        <v>584391</v>
       </c>
       <c r="R17" t="n">
-        <v>6320921</v>
+        <v>6320923</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2639,36 +2623,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841518</v>
+        <v>122841088</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2703,7 +2698,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2718,14 +2713,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584376</v>
+        <v>584332</v>
       </c>
       <c r="R18" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2784,7 +2779,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851716</v>
+        <v>122841328</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2817,28 +2812,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584419</v>
+        <v>584336</v>
       </c>
       <c r="R19" t="n">
-        <v>6320935</v>
+        <v>6320932</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2865,19 +2852,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,26 +2868,25 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851869</v>
+        <v>122840605</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2938,28 +2919,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584369</v>
+        <v>584384</v>
       </c>
       <c r="R20" t="n">
-        <v>6320904</v>
+        <v>6320873</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2986,47 +2959,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851575</v>
+        <v>122841069</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3059,28 +3021,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584415</v>
+        <v>584349</v>
       </c>
       <c r="R21" t="n">
-        <v>6320915</v>
+        <v>6320925</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3107,19 +3061,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3128,26 +3077,25 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851811</v>
+        <v>122851623</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3182,7 +3130,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3195,10 +3143,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584350</v>
+        <v>584406</v>
       </c>
       <c r="R22" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3268,10 +3216,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840797</v>
+        <v>122841954</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3280,38 +3228,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584406</v>
+        <v>584450</v>
       </c>
       <c r="R23" t="n">
-        <v>6320860</v>
+        <v>6321001</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3370,10 +3322,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122840491</v>
+        <v>122851862</v>
       </c>
       <c r="B24" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3382,41 +3334,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584478</v>
+        <v>584360</v>
       </c>
       <c r="R24" t="n">
-        <v>6320912</v>
+        <v>6320915</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3443,39 +3403,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851640</v>
+        <v>122841409</v>
       </c>
       <c r="B25" t="n">
-        <v>105471</v>
+        <v>57369</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3484,46 +3455,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584396</v>
+        <v>584384</v>
       </c>
       <c r="R25" t="n">
-        <v>6320930</v>
+        <v>6320921</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3553,50 +3521,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122852003</v>
+        <v>122851575</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3605,39 +3562,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3645,10 +3598,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584646</v>
+        <v>584415</v>
       </c>
       <c r="R26" t="n">
-        <v>6320922</v>
+        <v>6320915</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3699,6 +3652,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3717,10 +3671,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840605</v>
+        <v>122840491</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3729,38 +3683,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584384</v>
+        <v>584478</v>
       </c>
       <c r="R27" t="n">
-        <v>6320873</v>
+        <v>6320912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3807,22 +3761,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851741</v>
+        <v>122841878</v>
       </c>
       <c r="B28" t="n">
-        <v>57848</v>
+        <v>105471</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3835,49 +3789,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584357</v>
+        <v>584427</v>
       </c>
       <c r="R28" t="n">
-        <v>6320937</v>
+        <v>6320982</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3904,19 +3846,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3931,22 +3863,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851599</v>
+        <v>122839339</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3955,49 +3887,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584395</v>
+        <v>584548</v>
       </c>
       <c r="R29" t="n">
-        <v>6320916</v>
+        <v>6320905</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4024,50 +3948,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851829</v>
+        <v>122851605</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4076,30 +3989,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4112,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584348</v>
+        <v>584395</v>
       </c>
       <c r="R30" t="n">
-        <v>6320915</v>
+        <v>6320916</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4185,10 +4098,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122841088</v>
+        <v>122851504</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4197,55 +4110,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584332</v>
+        <v>584532</v>
       </c>
       <c r="R31" t="n">
-        <v>6320935</v>
+        <v>6320881</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4272,36 +4175,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841582</v>
+        <v>122841912</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4336,7 +4250,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4355,10 +4269,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584345</v>
+        <v>584384</v>
       </c>
       <c r="R32" t="n">
-        <v>6320948</v>
+        <v>6320970</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4417,10 +4331,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122839339</v>
+        <v>122851829</v>
       </c>
       <c r="B33" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4429,41 +4343,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584548</v>
+        <v>584348</v>
       </c>
       <c r="R33" t="n">
-        <v>6320905</v>
+        <v>6320915</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4490,39 +4412,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122852007</v>
+        <v>122851479</v>
       </c>
       <c r="B34" t="n">
-        <v>57484</v>
+        <v>58156</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4531,20 +4464,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4554,14 +4487,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4571,10 +4504,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584646</v>
+        <v>584584</v>
       </c>
       <c r="R34" t="n">
-        <v>6320922</v>
+        <v>6320910</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4643,10 +4576,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841954</v>
+        <v>122841596</v>
       </c>
       <c r="B35" t="n">
-        <v>90972</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4659,41 +4592,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584450</v>
+        <v>584389</v>
       </c>
       <c r="R35" t="n">
-        <v>6321001</v>
+        <v>6320931</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4723,6 +4652,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4737,22 +4671,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851479</v>
+        <v>122841582</v>
       </c>
       <c r="B36" t="n">
-        <v>58156</v>
+        <v>98365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4761,53 +4695,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584584</v>
+        <v>584345</v>
       </c>
       <c r="R36" t="n">
-        <v>6320910</v>
+        <v>6320948</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4834,19 +4770,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4861,19 +4787,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841533</v>
+        <v>122841855</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4909,17 +4835,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584369</v>
+        <v>584419</v>
       </c>
       <c r="R37" t="n">
-        <v>6320926</v>
+        <v>6320986</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4949,11 +4875,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,7 +4901,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851735</v>
+        <v>122841518</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -5015,26 +4936,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584357</v>
+        <v>584376</v>
       </c>
       <c r="R38" t="n">
         <v>6320937</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5061,50 +4988,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851562</v>
+        <v>122851599</v>
       </c>
       <c r="B39" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5113,30 +5029,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5149,10 +5065,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584415</v>
+        <v>584395</v>
       </c>
       <c r="R39" t="n">
-        <v>6320915</v>
+        <v>6320916</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5222,10 +5138,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122839920</v>
+        <v>122851540</v>
       </c>
       <c r="B40" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,41 +5150,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584525</v>
+        <v>584425</v>
       </c>
       <c r="R40" t="n">
-        <v>6320880</v>
+        <v>6320900</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,14 +5219,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5311,28 +5240,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851504</v>
+        <v>122851724</v>
       </c>
       <c r="B41" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5341,28 +5271,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -5373,10 +5307,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584532</v>
+        <v>584375</v>
       </c>
       <c r="R41" t="n">
-        <v>6320881</v>
+        <v>6320924</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5446,7 +5380,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851623</v>
+        <v>122851927</v>
       </c>
       <c r="B42" t="n">
         <v>98365</v>
@@ -5481,7 +5415,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -5494,10 +5428,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584406</v>
+        <v>584411</v>
       </c>
       <c r="R42" t="n">
-        <v>6320924</v>
+        <v>6320904</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5567,10 +5501,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851783</v>
+        <v>122851869</v>
       </c>
       <c r="B43" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5579,39 +5513,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5619,10 +5549,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584336</v>
+        <v>584369</v>
       </c>
       <c r="R43" t="n">
-        <v>6320920</v>
+        <v>6320904</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5673,6 +5603,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5691,7 +5622,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840279</v>
+        <v>122851640</v>
       </c>
       <c r="B44" t="n">
         <v>105471</v>
@@ -5726,22 +5657,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584419</v>
+        <v>584396</v>
       </c>
       <c r="R44" t="n">
-        <v>6320836</v>
+        <v>6320930</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5768,39 +5703,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122839190</v>
+        <v>122839920</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5809,25 +5755,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5837,10 +5783,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584581</v>
+        <v>584525</v>
       </c>
       <c r="R45" t="n">
-        <v>6320913</v>
+        <v>6320880</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5873,6 +5819,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5899,10 +5850,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841069</v>
+        <v>122851783</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5911,41 +5862,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584349</v>
+        <v>584336</v>
       </c>
       <c r="R46" t="n">
-        <v>6320925</v>
+        <v>6320920</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5972,14 +5935,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5994,19 +5962,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851724</v>
+        <v>122851716</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -6041,7 +6009,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6054,10 +6022,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584375</v>
+        <v>584419</v>
       </c>
       <c r="R47" t="n">
-        <v>6320924</v>
+        <v>6320935</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6127,7 +6095,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851540</v>
+        <v>122842080</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6160,28 +6128,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584425</v>
+        <v>584434</v>
       </c>
       <c r="R48" t="n">
-        <v>6320900</v>
+        <v>6320937</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6208,50 +6168,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851756</v>
+        <v>122851741</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6260,35 +6209,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6296,10 +6249,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584359</v>
+        <v>584357</v>
       </c>
       <c r="R49" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6350,7 +6303,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6490,10 +6442,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851590</v>
+        <v>122852007</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>57484</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6502,35 +6454,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6538,10 +6494,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584409</v>
+        <v>584646</v>
       </c>
       <c r="R51" t="n">
-        <v>6320920</v>
+        <v>6320922</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6592,7 +6548,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6611,7 +6566,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851662</v>
+        <v>122851756</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6646,7 +6601,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -6659,10 +6614,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584391</v>
+        <v>584359</v>
       </c>
       <c r="R52" t="n">
-        <v>6320923</v>
+        <v>6320919</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6732,7 +6687,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841328</v>
+        <v>122851735</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6765,20 +6720,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584336</v>
+        <v>584357</v>
       </c>
       <c r="R53" t="n">
-        <v>6320932</v>
+        <v>6320937</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6805,14 +6768,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6821,25 +6789,26 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122841855</v>
+        <v>122851811</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6872,20 +6841,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584419</v>
+        <v>584350</v>
       </c>
       <c r="R54" t="n">
-        <v>6320986</v>
+        <v>6320916</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6912,39 +6889,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851605</v>
+        <v>122841533</v>
       </c>
       <c r="B55" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6953,49 +6941,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584395</v>
+        <v>584369</v>
       </c>
       <c r="R55" t="n">
-        <v>6320916</v>
+        <v>6320926</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7022,19 +7002,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7043,26 +7018,25 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841596</v>
+        <v>122852003</v>
       </c>
       <c r="B56" t="n">
         <v>57494</v>
@@ -7095,20 +7069,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584389</v>
+        <v>584646</v>
       </c>
       <c r="R56" t="n">
-        <v>6320931</v>
+        <v>6320922</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7135,14 +7121,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7157,22 +7148,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851862</v>
+        <v>122840279</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7181,49 +7172,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584360</v>
+        <v>584419</v>
       </c>
       <c r="R57" t="n">
-        <v>6320915</v>
+        <v>6320836</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7250,50 +7237,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841878</v>
+        <v>122840797</v>
       </c>
       <c r="B58" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7302,41 +7278,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584427</v>
+        <v>584406</v>
       </c>
       <c r="R58" t="n">
-        <v>6320982</v>
+        <v>6320860</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7380,22 +7356,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122842080</v>
+        <v>122851562</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7404,41 +7380,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584434</v>
+        <v>584415</v>
       </c>
       <c r="R59" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7465,36 +7449,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122841912</v>
+        <v>122851590</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7529,32 +7524,26 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584384</v>
+        <v>584409</v>
       </c>
       <c r="R60" t="n">
-        <v>6320970</v>
+        <v>6320920</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7581,29 +7570,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -3216,10 +3216,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841954</v>
+        <v>122851862</v>
       </c>
       <c r="B23" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3228,45 +3228,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584450</v>
+        <v>584360</v>
       </c>
       <c r="R23" t="n">
-        <v>6321001</v>
+        <v>6320915</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3293,39 +3297,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851862</v>
+        <v>122841954</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3334,49 +3349,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584360</v>
+        <v>584450</v>
       </c>
       <c r="R24" t="n">
-        <v>6320915</v>
+        <v>6321001</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3403,40 +3414,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851756</v>
+        <v>122851735</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584359</v>
+        <v>584357</v>
       </c>
       <c r="R52" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851735</v>
+        <v>122851756</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584357</v>
+        <v>584359</v>
       </c>
       <c r="R53" t="n">
-        <v>6320937</v>
+        <v>6320919</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,7 +2440,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122839190</v>
+        <v>122851623</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2473,20 +2473,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584581</v>
+        <v>584406</v>
       </c>
       <c r="R16" t="n">
-        <v>6320913</v>
+        <v>6320924</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,29 +2521,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2779,7 +2798,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841328</v>
+        <v>122839190</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2819,10 +2838,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584336</v>
+        <v>584581</v>
       </c>
       <c r="R19" t="n">
-        <v>6320932</v>
+        <v>6320913</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2855,11 +2874,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2886,7 +2900,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122840605</v>
+        <v>122841328</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2926,13 +2940,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584384</v>
+        <v>584336</v>
       </c>
       <c r="R20" t="n">
-        <v>6320873</v>
+        <v>6320932</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2962,6 +2976,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,7 +3007,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841069</v>
+        <v>122840605</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3028,13 +3047,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584349</v>
+        <v>584384</v>
       </c>
       <c r="R21" t="n">
-        <v>6320925</v>
+        <v>6320873</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3064,11 +3083,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,7 +3109,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851623</v>
+        <v>122841069</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3128,28 +3142,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584406</v>
+        <v>584349</v>
       </c>
       <c r="R22" t="n">
-        <v>6320924</v>
+        <v>6320925</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3176,19 +3182,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3197,29 +3198,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851862</v>
+        <v>122841954</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3228,49 +3228,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584360</v>
+        <v>584450</v>
       </c>
       <c r="R23" t="n">
-        <v>6320915</v>
+        <v>6321001</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3297,50 +3293,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841954</v>
+        <v>122851862</v>
       </c>
       <c r="B24" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3349,45 +3334,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584450</v>
+        <v>584360</v>
       </c>
       <c r="R24" t="n">
-        <v>6321001</v>
+        <v>6320915</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3414,29 +3403,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4799,7 +4799,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841855</v>
+        <v>122841518</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4832,20 +4832,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584419</v>
+        <v>584376</v>
       </c>
       <c r="R37" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4889,19 +4903,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841518</v>
+        <v>122841855</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4934,34 +4948,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584376</v>
+        <v>584419</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320986</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5005,12 +5005,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851869</v>
+        <v>122839920</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5513,49 +5513,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584369</v>
+        <v>584525</v>
       </c>
       <c r="R43" t="n">
-        <v>6320904</v>
+        <v>6320880</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5582,19 +5574,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5603,19 +5590,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5743,10 +5729,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122839920</v>
+        <v>122851869</v>
       </c>
       <c r="B45" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5755,41 +5741,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R45" t="n">
-        <v>6320880</v>
+        <v>6320904</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5816,14 +5810,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5832,18 +5831,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,7 +2440,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851623</v>
+        <v>122851599</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584406</v>
+        <v>584395</v>
       </c>
       <c r="R16" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2561,10 +2561,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851662</v>
+        <v>122841596</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,49 +2573,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584391</v>
+        <v>584389</v>
       </c>
       <c r="R17" t="n">
-        <v>6320923</v>
+        <v>6320931</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2642,19 +2634,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2663,29 +2650,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841088</v>
+        <v>122851479</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>58156</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2694,55 +2680,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584332</v>
+        <v>584584</v>
       </c>
       <c r="R18" t="n">
-        <v>6320935</v>
+        <v>6320910</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2769,9 +2753,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,19 +2780,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122839190</v>
+        <v>122851716</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2831,20 +2825,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584581</v>
+        <v>584419</v>
       </c>
       <c r="R19" t="n">
-        <v>6320913</v>
+        <v>6320935</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2871,39 +2873,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841328</v>
+        <v>122839339</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2912,41 +2925,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584336</v>
+        <v>584548</v>
       </c>
       <c r="R20" t="n">
-        <v>6320932</v>
+        <v>6320905</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2976,11 +2989,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2995,22 +3003,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122840605</v>
+        <v>122841409</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3019,28 +3027,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
@@ -3050,10 +3063,10 @@
         <v>584384</v>
       </c>
       <c r="R21" t="n">
-        <v>6320873</v>
+        <v>6320921</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3109,10 +3122,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841069</v>
+        <v>122840279</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3121,38 +3134,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584349</v>
+        <v>584419</v>
       </c>
       <c r="R22" t="n">
-        <v>6320925</v>
+        <v>6320836</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3185,11 +3202,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3216,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841954</v>
+        <v>122841878</v>
       </c>
       <c r="B23" t="n">
-        <v>90972</v>
+        <v>105471</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3228,45 +3240,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584450</v>
+        <v>584427</v>
       </c>
       <c r="R23" t="n">
-        <v>6321001</v>
+        <v>6320982</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3310,22 +3318,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851862</v>
+        <v>122852007</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>57484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3334,35 +3342,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3370,10 +3382,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584360</v>
+        <v>584646</v>
       </c>
       <c r="R24" t="n">
-        <v>6320915</v>
+        <v>6320922</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3424,7 +3436,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3443,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841409</v>
+        <v>122841088</v>
       </c>
       <c r="B25" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3455,46 +3466,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584384</v>
+        <v>584332</v>
       </c>
       <c r="R25" t="n">
-        <v>6320921</v>
+        <v>6320935</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3538,19 +3558,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851575</v>
+        <v>122841912</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3585,26 +3605,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R26" t="n">
-        <v>6320915</v>
+        <v>6320970</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3631,50 +3657,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840491</v>
+        <v>122851756</v>
       </c>
       <c r="B27" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3683,41 +3698,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584478</v>
+        <v>584359</v>
       </c>
       <c r="R27" t="n">
-        <v>6320912</v>
+        <v>6320919</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3744,39 +3767,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841878</v>
+        <v>122851811</v>
       </c>
       <c r="B28" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3785,41 +3819,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584427</v>
+        <v>584350</v>
       </c>
       <c r="R28" t="n">
-        <v>6320982</v>
+        <v>6320916</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3846,39 +3888,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122839339</v>
+        <v>122841954</v>
       </c>
       <c r="B29" t="n">
-        <v>95136</v>
+        <v>90972</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3887,41 +3940,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584548</v>
+        <v>584450</v>
       </c>
       <c r="R29" t="n">
-        <v>6320905</v>
+        <v>6321001</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3977,10 +4034,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851605</v>
+        <v>122851623</v>
       </c>
       <c r="B30" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3989,30 +4046,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4025,10 +4082,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584395</v>
+        <v>584406</v>
       </c>
       <c r="R30" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4098,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851504</v>
+        <v>122851605</v>
       </c>
       <c r="B31" t="n">
-        <v>95136</v>
+        <v>105471</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4114,24 +4171,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -4142,10 +4203,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R31" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4215,10 +4276,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841912</v>
+        <v>122851783</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4227,55 +4288,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584384</v>
+        <v>584336</v>
       </c>
       <c r="R32" t="n">
-        <v>6320970</v>
+        <v>6320920</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4302,9 +4361,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4319,19 +4388,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851829</v>
+        <v>122851575</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4366,7 +4435,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4379,7 +4448,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584348</v>
+        <v>584415</v>
       </c>
       <c r="R33" t="n">
         <v>6320915</v>
@@ -4452,10 +4521,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851479</v>
+        <v>122840491</v>
       </c>
       <c r="B34" t="n">
-        <v>58156</v>
+        <v>95136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4468,49 +4537,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584584</v>
+        <v>584478</v>
       </c>
       <c r="R34" t="n">
-        <v>6320910</v>
+        <v>6320912</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4537,19 +4594,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4564,22 +4611,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841596</v>
+        <v>122841069</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4588,38 +4635,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584389</v>
+        <v>584349</v>
       </c>
       <c r="R35" t="n">
-        <v>6320931</v>
+        <v>6320925</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4656,7 +4703,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4683,7 +4730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841582</v>
+        <v>122839190</v>
       </c>
       <c r="B36" t="n">
         <v>98365</v>
@@ -4716,34 +4763,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584345</v>
+        <v>584581</v>
       </c>
       <c r="R36" t="n">
-        <v>6320948</v>
+        <v>6320913</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4787,19 +4820,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841518</v>
+        <v>122841582</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4853,13 +4886,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584376</v>
+        <v>584345</v>
       </c>
       <c r="R37" t="n">
-        <v>6320937</v>
+        <v>6320948</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4915,7 +4948,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841855</v>
+        <v>122851540</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4948,20 +4981,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584419</v>
+        <v>584425</v>
       </c>
       <c r="R38" t="n">
-        <v>6320986</v>
+        <v>6320900</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4988,36 +5029,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851599</v>
+        <v>122851829</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5052,7 +5104,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5065,10 +5117,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584395</v>
+        <v>584348</v>
       </c>
       <c r="R39" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5138,7 +5190,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851540</v>
+        <v>122841533</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5171,28 +5223,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584425</v>
+        <v>584369</v>
       </c>
       <c r="R40" t="n">
-        <v>6320900</v>
+        <v>6320926</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5219,19 +5263,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5240,29 +5279,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851724</v>
+        <v>122852003</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5271,35 +5309,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5307,10 +5349,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584375</v>
+        <v>584646</v>
       </c>
       <c r="R41" t="n">
-        <v>6320924</v>
+        <v>6320922</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5361,7 +5403,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5380,10 +5421,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851927</v>
+        <v>122839920</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5392,49 +5433,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584411</v>
+        <v>584525</v>
       </c>
       <c r="R42" t="n">
-        <v>6320904</v>
+        <v>6320880</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5461,19 +5494,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5482,29 +5510,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122839920</v>
+        <v>122851735</v>
       </c>
       <c r="B43" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5513,41 +5540,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584525</v>
+        <v>584357</v>
       </c>
       <c r="R43" t="n">
-        <v>6320880</v>
+        <v>6320937</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5574,14 +5609,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5590,28 +5630,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851640</v>
+        <v>122851469</v>
       </c>
       <c r="B44" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5620,30 +5661,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5656,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584396</v>
+        <v>584584</v>
       </c>
       <c r="R44" t="n">
-        <v>6320930</v>
+        <v>6320910</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5729,7 +5770,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851869</v>
+        <v>122840605</v>
       </c>
       <c r="B45" t="n">
         <v>98365</v>
@@ -5762,28 +5803,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584369</v>
+        <v>584384</v>
       </c>
       <c r="R45" t="n">
-        <v>6320904</v>
+        <v>6320873</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5810,50 +5843,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851783</v>
+        <v>122851927</v>
       </c>
       <c r="B46" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5862,39 +5884,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5902,10 +5920,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584336</v>
+        <v>584411</v>
       </c>
       <c r="R46" t="n">
-        <v>6320920</v>
+        <v>6320904</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5956,6 +5974,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5974,7 +5993,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851716</v>
+        <v>122851724</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -6009,7 +6028,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6022,10 +6041,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R47" t="n">
-        <v>6320935</v>
+        <v>6320924</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6095,10 +6114,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122842080</v>
+        <v>122851640</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6107,41 +6126,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584434</v>
+        <v>584396</v>
       </c>
       <c r="R48" t="n">
-        <v>6320937</v>
+        <v>6320930</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6168,39 +6195,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851741</v>
+        <v>122851869</v>
       </c>
       <c r="B49" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6209,39 +6247,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6249,10 +6283,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584357</v>
+        <v>584369</v>
       </c>
       <c r="R49" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6303,6 +6337,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6321,7 +6356,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851469</v>
+        <v>122841328</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6354,28 +6389,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584584</v>
+        <v>584336</v>
       </c>
       <c r="R50" t="n">
-        <v>6320910</v>
+        <v>6320932</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6402,19 +6429,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6423,29 +6445,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122852007</v>
+        <v>122851590</v>
       </c>
       <c r="B51" t="n">
-        <v>57484</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6454,39 +6475,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6494,10 +6511,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584646</v>
+        <v>584409</v>
       </c>
       <c r="R51" t="n">
-        <v>6320922</v>
+        <v>6320920</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6548,6 +6565,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6566,10 +6584,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851735</v>
+        <v>122851562</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6578,30 +6596,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -6614,10 +6632,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584357</v>
+        <v>584415</v>
       </c>
       <c r="R52" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6687,7 +6705,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851756</v>
+        <v>122840797</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6720,28 +6738,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584359</v>
+        <v>584406</v>
       </c>
       <c r="R53" t="n">
-        <v>6320919</v>
+        <v>6320860</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6768,47 +6778,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851811</v>
+        <v>122842080</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6841,28 +6840,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584350</v>
+        <v>584434</v>
       </c>
       <c r="R54" t="n">
-        <v>6320916</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6889,47 +6880,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841533</v>
+        <v>122841855</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6965,17 +6945,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584369</v>
+        <v>584419</v>
       </c>
       <c r="R55" t="n">
-        <v>6320926</v>
+        <v>6320986</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7005,11 +6985,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7036,10 +7011,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122852003</v>
+        <v>122851504</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7048,39 +7023,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7088,10 +7055,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584646</v>
+        <v>584532</v>
       </c>
       <c r="R56" t="n">
-        <v>6320922</v>
+        <v>6320881</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7142,6 +7109,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7160,10 +7128,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122840279</v>
+        <v>122851662</v>
       </c>
       <c r="B57" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7172,45 +7140,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584419</v>
+        <v>584391</v>
       </c>
       <c r="R57" t="n">
-        <v>6320836</v>
+        <v>6320923</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7237,36 +7209,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840797</v>
+        <v>122841518</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -7299,17 +7282,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584406</v>
+        <v>584376</v>
       </c>
       <c r="R58" t="n">
-        <v>6320860</v>
+        <v>6320937</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7368,10 +7365,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851562</v>
+        <v>122851862</v>
       </c>
       <c r="B59" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7380,30 +7377,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -7416,7 +7413,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584415</v>
+        <v>584360</v>
       </c>
       <c r="R59" t="n">
         <v>6320915</v>
@@ -7489,10 +7486,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851590</v>
+        <v>122851741</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7501,25 +7498,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7527,9 +7524,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7537,10 +7538,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584409</v>
+        <v>584357</v>
       </c>
       <c r="R60" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7591,7 +7592,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851599</v>
+        <v>122841409</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,46 +2452,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584395</v>
+        <v>584384</v>
       </c>
       <c r="R16" t="n">
-        <v>6320916</v>
+        <v>6320921</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2521,50 +2518,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841596</v>
+        <v>122851735</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,41 +2559,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584389</v>
+        <v>584357</v>
       </c>
       <c r="R17" t="n">
-        <v>6320931</v>
+        <v>6320937</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2634,14 +2628,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2650,28 +2649,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851479</v>
+        <v>122841328</v>
       </c>
       <c r="B18" t="n">
-        <v>58156</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,53 +2680,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584584</v>
+        <v>584336</v>
       </c>
       <c r="R18" t="n">
-        <v>6320910</v>
+        <v>6320932</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2753,19 +2741,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2780,19 +2763,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851716</v>
+        <v>122851540</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2827,7 +2810,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2840,10 +2823,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584419</v>
+        <v>584425</v>
       </c>
       <c r="R19" t="n">
-        <v>6320935</v>
+        <v>6320900</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2913,7 +2896,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122839339</v>
+        <v>122840491</v>
       </c>
       <c r="B20" t="n">
         <v>95136</v>
@@ -2949,17 +2932,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584548</v>
+        <v>584478</v>
       </c>
       <c r="R20" t="n">
-        <v>6320905</v>
+        <v>6320912</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3015,7 +2998,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841409</v>
+        <v>122851783</v>
       </c>
       <c r="B21" t="n">
         <v>57369</v>
@@ -3048,22 +3031,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584384</v>
+        <v>584336</v>
       </c>
       <c r="R21" t="n">
-        <v>6320921</v>
+        <v>6320920</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3093,9 +3083,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,22 +3110,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840279</v>
+        <v>122840797</v>
       </c>
       <c r="B22" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3134,45 +3134,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584419</v>
+        <v>584406</v>
       </c>
       <c r="R22" t="n">
-        <v>6320836</v>
+        <v>6320860</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3216,22 +3212,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841878</v>
+        <v>122851724</v>
       </c>
       <c r="B23" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3240,41 +3236,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584427</v>
+        <v>584375</v>
       </c>
       <c r="R23" t="n">
-        <v>6320982</v>
+        <v>6320924</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3301,39 +3305,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122852007</v>
+        <v>122841954</v>
       </c>
       <c r="B24" t="n">
-        <v>57484</v>
+        <v>90972</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3346,21 +3361,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3368,27 +3383,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584646</v>
+        <v>584450</v>
       </c>
       <c r="R24" t="n">
-        <v>6320922</v>
+        <v>6321001</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3415,19 +3422,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3442,19 +3439,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841088</v>
+        <v>122842080</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3487,31 +3484,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584332</v>
+        <v>584434</v>
       </c>
       <c r="R25" t="n">
-        <v>6320935</v>
+        <v>6320937</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3558,19 +3541,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841912</v>
+        <v>122840605</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3603,34 +3586,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
         <v>584384</v>
       </c>
       <c r="R26" t="n">
-        <v>6320970</v>
+        <v>6320873</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3674,22 +3643,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851756</v>
+        <v>122851479</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>58156</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3698,35 +3667,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3734,10 +3707,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584359</v>
+        <v>584584</v>
       </c>
       <c r="R27" t="n">
-        <v>6320919</v>
+        <v>6320910</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3788,7 +3761,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3807,7 +3779,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851811</v>
+        <v>122851662</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3842,7 +3814,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3855,10 +3827,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584350</v>
+        <v>584391</v>
       </c>
       <c r="R28" t="n">
-        <v>6320916</v>
+        <v>6320923</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3928,10 +3900,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841954</v>
+        <v>122851716</v>
       </c>
       <c r="B29" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3940,45 +3912,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584450</v>
+        <v>584419</v>
       </c>
       <c r="R29" t="n">
-        <v>6321001</v>
+        <v>6320935</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4005,36 +3981,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851623</v>
+        <v>122851599</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -4069,7 +4056,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4082,10 +4069,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584406</v>
+        <v>584395</v>
       </c>
       <c r="R30" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4155,10 +4142,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851605</v>
+        <v>122851862</v>
       </c>
       <c r="B31" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4167,30 +4154,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4203,10 +4190,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584395</v>
+        <v>584360</v>
       </c>
       <c r="R31" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4276,10 +4263,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851783</v>
+        <v>122851562</v>
       </c>
       <c r="B32" t="n">
-        <v>57369</v>
+        <v>105471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4288,39 +4275,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4328,10 +4311,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584336</v>
+        <v>584415</v>
       </c>
       <c r="R32" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4382,6 +4365,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4400,10 +4384,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851575</v>
+        <v>122839339</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4412,49 +4396,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584415</v>
+        <v>584548</v>
       </c>
       <c r="R33" t="n">
-        <v>6320915</v>
+        <v>6320905</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4481,50 +4457,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840491</v>
+        <v>122851575</v>
       </c>
       <c r="B34" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4533,41 +4498,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584478</v>
+        <v>584415</v>
       </c>
       <c r="R34" t="n">
-        <v>6320912</v>
+        <v>6320915</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4594,39 +4567,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841069</v>
+        <v>122839920</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4635,25 +4619,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4663,10 +4647,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584349</v>
+        <v>584525</v>
       </c>
       <c r="R35" t="n">
-        <v>6320925</v>
+        <v>6320880</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4703,7 +4687,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>50-tal plantor</t>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4730,10 +4714,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122839190</v>
+        <v>122841596</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4742,38 +4726,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584581</v>
+        <v>584389</v>
       </c>
       <c r="R36" t="n">
-        <v>6320913</v>
+        <v>6320931</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4806,6 +4790,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4832,10 +4821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841582</v>
+        <v>122852003</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4844,55 +4833,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584345</v>
+        <v>584646</v>
       </c>
       <c r="R37" t="n">
-        <v>6320948</v>
+        <v>6320922</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4919,9 +4906,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4936,19 +4933,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851540</v>
+        <v>122851623</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4983,7 +4980,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4996,10 +4993,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584425</v>
+        <v>584406</v>
       </c>
       <c r="R38" t="n">
-        <v>6320900</v>
+        <v>6320924</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5069,7 +5066,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851829</v>
+        <v>122851590</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5104,7 +5101,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5117,10 +5114,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584348</v>
+        <v>584409</v>
       </c>
       <c r="R39" t="n">
-        <v>6320915</v>
+        <v>6320920</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5190,7 +5187,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841533</v>
+        <v>122851756</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5223,20 +5220,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584369</v>
+        <v>584359</v>
       </c>
       <c r="R40" t="n">
-        <v>6320926</v>
+        <v>6320919</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5263,14 +5268,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5279,28 +5289,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122852003</v>
+        <v>122852007</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>57484</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5313,16 +5324,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5421,10 +5432,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122839920</v>
+        <v>122841518</v>
       </c>
       <c r="B42" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5433,41 +5444,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584525</v>
+        <v>584376</v>
       </c>
       <c r="R42" t="n">
-        <v>6320880</v>
+        <v>6320937</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5497,11 +5522,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5516,22 +5536,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851735</v>
+        <v>122840279</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5540,49 +5560,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R43" t="n">
-        <v>6320937</v>
+        <v>6320836</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5609,47 +5625,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851469</v>
+        <v>122841912</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5684,26 +5689,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584584</v>
+        <v>584384</v>
       </c>
       <c r="R44" t="n">
-        <v>6320910</v>
+        <v>6320970</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5730,50 +5741,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840605</v>
+        <v>122851504</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5782,41 +5782,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584384</v>
+        <v>584532</v>
       </c>
       <c r="R45" t="n">
-        <v>6320873</v>
+        <v>6320881</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5843,39 +5847,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851927</v>
+        <v>122851640</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5884,30 +5899,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5920,10 +5935,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584411</v>
+        <v>584396</v>
       </c>
       <c r="R46" t="n">
-        <v>6320904</v>
+        <v>6320930</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5993,10 +6008,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851724</v>
+        <v>122851605</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6005,30 +6020,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6041,10 +6056,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584375</v>
+        <v>584395</v>
       </c>
       <c r="R47" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6114,10 +6129,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851640</v>
+        <v>122839190</v>
       </c>
       <c r="B48" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6126,49 +6141,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584396</v>
+        <v>584581</v>
       </c>
       <c r="R48" t="n">
-        <v>6320930</v>
+        <v>6320913</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6195,50 +6202,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851869</v>
+        <v>122841878</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6247,49 +6243,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584369</v>
+        <v>584427</v>
       </c>
       <c r="R49" t="n">
-        <v>6320904</v>
+        <v>6320982</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6316,47 +6304,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841328</v>
+        <v>122841582</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6389,20 +6366,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584336</v>
+        <v>584345</v>
       </c>
       <c r="R50" t="n">
-        <v>6320932</v>
+        <v>6320948</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6432,11 +6423,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6451,22 +6437,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851590</v>
+        <v>122851741</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6475,25 +6461,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6501,9 +6487,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6511,10 +6501,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584409</v>
+        <v>584357</v>
       </c>
       <c r="R51" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6565,7 +6555,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6584,10 +6573,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851562</v>
+        <v>122841855</v>
       </c>
       <c r="B52" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6596,49 +6585,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584415</v>
+        <v>584419</v>
       </c>
       <c r="R52" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6665,47 +6646,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122840797</v>
+        <v>122851869</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6738,20 +6708,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584406</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320860</v>
+        <v>6320904</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6778,36 +6756,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122842080</v>
+        <v>122851829</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6840,20 +6829,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584434</v>
+        <v>584348</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6880,36 +6877,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841855</v>
+        <v>122851469</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6942,20 +6950,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R55" t="n">
-        <v>6320986</v>
+        <v>6320910</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6982,39 +6998,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851504</v>
+        <v>122851811</v>
       </c>
       <c r="B56" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7023,28 +7050,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -7055,10 +7086,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584532</v>
+        <v>584350</v>
       </c>
       <c r="R56" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7128,7 +7159,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851662</v>
+        <v>122841069</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -7161,28 +7192,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584391</v>
+        <v>584349</v>
       </c>
       <c r="R57" t="n">
-        <v>6320923</v>
+        <v>6320925</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7209,19 +7232,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7230,26 +7248,25 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841518</v>
+        <v>122841088</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -7284,7 +7301,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7299,14 +7316,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584376</v>
+        <v>584332</v>
       </c>
       <c r="R58" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7365,7 +7382,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851862</v>
+        <v>122841533</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7398,28 +7415,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584360</v>
+        <v>584369</v>
       </c>
       <c r="R59" t="n">
-        <v>6320915</v>
+        <v>6320926</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7446,19 +7455,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7467,29 +7471,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851741</v>
+        <v>122851927</v>
       </c>
       <c r="B60" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7498,39 +7501,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7538,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584357</v>
+        <v>584411</v>
       </c>
       <c r="R60" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7592,6 +7591,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122841409</v>
+        <v>122851735</v>
       </c>
       <c r="B16" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,43 +2452,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R16" t="n">
-        <v>6320921</v>
+        <v>6320937</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2518,39 +2521,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851735</v>
+        <v>122841409</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2559,46 +2573,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R17" t="n">
-        <v>6320937</v>
+        <v>6320921</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2628,40 +2639,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122839339</v>
+        <v>122851575</v>
       </c>
       <c r="B33" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4396,41 +4396,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584548</v>
+        <v>584415</v>
       </c>
       <c r="R33" t="n">
-        <v>6320905</v>
+        <v>6320915</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4457,39 +4465,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851575</v>
+        <v>122839339</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4498,49 +4517,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584415</v>
+        <v>584548</v>
       </c>
       <c r="R34" t="n">
-        <v>6320915</v>
+        <v>6320905</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4567,40 +4578,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122852003</v>
+        <v>122851623</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4833,39 +4833,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4873,10 +4869,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584646</v>
+        <v>584406</v>
       </c>
       <c r="R37" t="n">
-        <v>6320922</v>
+        <v>6320924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4927,6 +4923,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4945,7 +4942,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851623</v>
+        <v>122851590</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4980,7 +4977,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4993,10 +4990,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584406</v>
+        <v>584409</v>
       </c>
       <c r="R38" t="n">
-        <v>6320924</v>
+        <v>6320920</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5066,10 +5063,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851590</v>
+        <v>122852003</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5078,35 +5075,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5114,10 +5115,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584409</v>
+        <v>584646</v>
       </c>
       <c r="R39" t="n">
-        <v>6320920</v>
+        <v>6320922</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5168,7 +5169,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851756</v>
+        <v>122852007</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>57484</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5199,35 +5199,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5235,10 +5239,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584359</v>
+        <v>584646</v>
       </c>
       <c r="R40" t="n">
-        <v>6320919</v>
+        <v>6320922</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5289,7 +5293,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5308,10 +5311,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122852007</v>
+        <v>122851756</v>
       </c>
       <c r="B41" t="n">
-        <v>57484</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5320,39 +5323,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5360,10 +5359,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584646</v>
+        <v>584359</v>
       </c>
       <c r="R41" t="n">
-        <v>6320922</v>
+        <v>6320919</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5414,6 +5413,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851504</v>
+        <v>122851640</v>
       </c>
       <c r="B45" t="n">
-        <v>95136</v>
+        <v>105471</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5786,24 +5786,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -5814,10 +5818,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584532</v>
+        <v>584396</v>
       </c>
       <c r="R45" t="n">
-        <v>6320881</v>
+        <v>6320930</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5887,7 +5891,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851640</v>
+        <v>122851605</v>
       </c>
       <c r="B46" t="n">
         <v>105471</v>
@@ -5922,7 +5926,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5935,10 +5939,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584396</v>
+        <v>584395</v>
       </c>
       <c r="R46" t="n">
-        <v>6320930</v>
+        <v>6320916</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6008,10 +6012,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851605</v>
+        <v>122851504</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6024,28 +6028,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584395</v>
+        <v>584532</v>
       </c>
       <c r="R47" t="n">
-        <v>6320916</v>
+        <v>6320881</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122839190</v>
+        <v>122841582</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6162,20 +6162,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584581</v>
+        <v>584345</v>
       </c>
       <c r="R48" t="n">
-        <v>6320913</v>
+        <v>6320948</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6219,22 +6233,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841878</v>
+        <v>122839190</v>
       </c>
       <c r="B49" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6243,41 +6257,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584427</v>
+        <v>584581</v>
       </c>
       <c r="R49" t="n">
-        <v>6320982</v>
+        <v>6320913</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6333,10 +6347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841582</v>
+        <v>122841878</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6345,52 +6359,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584345</v>
+        <v>584427</v>
       </c>
       <c r="R50" t="n">
-        <v>6320948</v>
+        <v>6320982</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6437,22 +6437,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851741</v>
+        <v>122851869</v>
       </c>
       <c r="B51" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6461,39 +6461,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6501,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584357</v>
+        <v>584369</v>
       </c>
       <c r="R51" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6555,6 +6551,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6573,7 +6570,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841855</v>
+        <v>122851829</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6606,20 +6603,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584419</v>
+        <v>584348</v>
       </c>
       <c r="R52" t="n">
-        <v>6320986</v>
+        <v>6320915</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6646,36 +6651,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851869</v>
+        <v>122851469</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6710,7 +6726,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6723,10 +6739,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584584</v>
       </c>
       <c r="R53" t="n">
-        <v>6320904</v>
+        <v>6320910</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6796,10 +6812,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851829</v>
+        <v>122851741</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6808,35 +6824,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6844,10 +6864,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584348</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6898,7 +6918,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6917,7 +6936,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851469</v>
+        <v>122841855</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6950,28 +6969,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R55" t="n">
-        <v>6320910</v>
+        <v>6320986</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6998,40 +7009,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2668,7 +2668,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841328</v>
+        <v>122851540</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2701,20 +2701,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R18" t="n">
-        <v>6320932</v>
+        <v>6320900</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2741,14 +2749,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2757,25 +2770,26 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851540</v>
+        <v>122841328</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2808,28 +2822,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584425</v>
+        <v>584336</v>
       </c>
       <c r="R19" t="n">
-        <v>6320900</v>
+        <v>6320932</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2856,19 +2862,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2877,19 +2878,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851623</v>
+        <v>122852003</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4833,35 +4833,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4869,10 +4873,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584406</v>
+        <v>584646</v>
       </c>
       <c r="R37" t="n">
-        <v>6320924</v>
+        <v>6320922</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4923,7 +4927,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4942,7 +4945,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851590</v>
+        <v>122851623</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4977,7 +4980,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4990,10 +4993,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584409</v>
+        <v>584406</v>
       </c>
       <c r="R38" t="n">
-        <v>6320920</v>
+        <v>6320924</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5063,10 +5066,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122852003</v>
+        <v>122851590</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5075,39 +5078,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5115,10 +5114,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584646</v>
+        <v>584409</v>
       </c>
       <c r="R39" t="n">
-        <v>6320922</v>
+        <v>6320920</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5169,6 +5168,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851640</v>
+        <v>122851504</v>
       </c>
       <c r="B45" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5786,28 +5786,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -5818,10 +5814,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584396</v>
+        <v>584532</v>
       </c>
       <c r="R45" t="n">
-        <v>6320930</v>
+        <v>6320881</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5891,7 +5887,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851605</v>
+        <v>122851640</v>
       </c>
       <c r="B46" t="n">
         <v>105471</v>
@@ -5926,7 +5922,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5939,10 +5935,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584395</v>
+        <v>584396</v>
       </c>
       <c r="R46" t="n">
-        <v>6320916</v>
+        <v>6320930</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6012,10 +6008,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851504</v>
+        <v>122851605</v>
       </c>
       <c r="B47" t="n">
-        <v>95136</v>
+        <v>105471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6028,24 +6024,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R47" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6449,10 +6449,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851869</v>
+        <v>122851741</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6461,35 +6461,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6497,10 +6501,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584369</v>
+        <v>584357</v>
       </c>
       <c r="R51" t="n">
-        <v>6320904</v>
+        <v>6320937</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6551,7 +6555,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6570,7 +6573,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851829</v>
+        <v>122841855</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6603,28 +6606,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R52" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6651,47 +6646,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851469</v>
+        <v>122851869</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6726,7 +6710,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6739,10 +6723,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584584</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320910</v>
+        <v>6320904</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6812,10 +6796,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851741</v>
+        <v>122851829</v>
       </c>
       <c r="B54" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6824,39 +6808,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6864,10 +6844,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584348</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6918,6 +6898,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6936,7 +6917,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841855</v>
+        <v>122851469</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6969,20 +6950,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R55" t="n">
-        <v>6320986</v>
+        <v>6320910</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7009,29 +6998,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -4821,10 +4821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122852003</v>
+        <v>122851623</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4833,39 +4833,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4873,10 +4869,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584646</v>
+        <v>584406</v>
       </c>
       <c r="R37" t="n">
-        <v>6320922</v>
+        <v>6320924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4927,6 +4923,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4945,7 +4942,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851623</v>
+        <v>122851590</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4980,7 +4977,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4993,10 +4990,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584406</v>
+        <v>584409</v>
       </c>
       <c r="R38" t="n">
-        <v>6320924</v>
+        <v>6320920</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5066,10 +5063,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851590</v>
+        <v>122852003</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5078,35 +5075,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5114,10 +5115,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584409</v>
+        <v>584646</v>
       </c>
       <c r="R39" t="n">
-        <v>6320920</v>
+        <v>6320922</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5168,7 +5169,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841582</v>
+        <v>122839190</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6162,34 +6162,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584345</v>
+        <v>584581</v>
       </c>
       <c r="R48" t="n">
-        <v>6320948</v>
+        <v>6320913</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6233,22 +6219,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122839190</v>
+        <v>122841878</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6257,41 +6243,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584581</v>
+        <v>584427</v>
       </c>
       <c r="R49" t="n">
-        <v>6320913</v>
+        <v>6320982</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6347,10 +6333,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841878</v>
+        <v>122841582</v>
       </c>
       <c r="B50" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6359,38 +6345,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584427</v>
+        <v>584345</v>
       </c>
       <c r="R50" t="n">
-        <v>6320982</v>
+        <v>6320948</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6437,12 +6437,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -4821,10 +4821,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851623</v>
+        <v>122852003</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4833,35 +4833,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4869,10 +4873,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584406</v>
+        <v>584646</v>
       </c>
       <c r="R37" t="n">
-        <v>6320924</v>
+        <v>6320922</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4923,7 +4927,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4942,7 +4945,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851590</v>
+        <v>122851623</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4977,7 +4980,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4990,10 +4993,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584409</v>
+        <v>584406</v>
       </c>
       <c r="R38" t="n">
-        <v>6320920</v>
+        <v>6320924</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5063,10 +5066,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122852003</v>
+        <v>122851590</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5075,39 +5078,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5115,10 +5114,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584646</v>
+        <v>584409</v>
       </c>
       <c r="R39" t="n">
-        <v>6320922</v>
+        <v>6320920</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5169,6 +5168,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122839190</v>
+        <v>122841582</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6162,20 +6162,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584581</v>
+        <v>584345</v>
       </c>
       <c r="R48" t="n">
-        <v>6320913</v>
+        <v>6320948</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6219,22 +6233,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841878</v>
+        <v>122839190</v>
       </c>
       <c r="B49" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6243,41 +6257,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584427</v>
+        <v>584581</v>
       </c>
       <c r="R49" t="n">
-        <v>6320982</v>
+        <v>6320913</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6333,10 +6347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841582</v>
+        <v>122841878</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6345,52 +6359,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584345</v>
+        <v>584427</v>
       </c>
       <c r="R50" t="n">
-        <v>6320948</v>
+        <v>6320982</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6437,12 +6437,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851735</v>
+        <v>122839920</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,49 +2452,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584357</v>
+        <v>584525</v>
       </c>
       <c r="R16" t="n">
-        <v>6320937</v>
+        <v>6320880</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2521,19 +2513,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2542,29 +2529,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122841409</v>
+        <v>122839190</v>
       </c>
       <c r="B17" t="n">
-        <v>57369</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2573,46 +2559,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584384</v>
+        <v>584581</v>
       </c>
       <c r="R17" t="n">
-        <v>6320921</v>
+        <v>6320913</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2668,10 +2649,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851540</v>
+        <v>122841409</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2680,46 +2661,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584425</v>
+        <v>584384</v>
       </c>
       <c r="R18" t="n">
-        <v>6320900</v>
+        <v>6320921</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2749,50 +2727,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841328</v>
+        <v>122851469</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2822,20 +2789,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584336</v>
+        <v>584584</v>
       </c>
       <c r="R19" t="n">
-        <v>6320932</v>
+        <v>6320910</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,14 +2837,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2878,28 +2858,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122840491</v>
+        <v>122841328</v>
       </c>
       <c r="B20" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2908,41 +2889,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584478</v>
+        <v>584336</v>
       </c>
       <c r="R20" t="n">
-        <v>6320912</v>
+        <v>6320932</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2972,6 +2953,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2986,22 +2972,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851783</v>
+        <v>122841069</v>
       </c>
       <c r="B21" t="n">
-        <v>57369</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3010,53 +2996,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584336</v>
+        <v>584349</v>
       </c>
       <c r="R21" t="n">
-        <v>6320920</v>
+        <v>6320925</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3083,19 +3057,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,22 +3079,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840797</v>
+        <v>122851811</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3155,20 +3124,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584406</v>
+        <v>584350</v>
       </c>
       <c r="R22" t="n">
-        <v>6320860</v>
+        <v>6320916</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3195,39 +3172,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851724</v>
+        <v>122851869</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3259,7 +3247,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3272,10 +3260,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584375</v>
+        <v>584369</v>
       </c>
       <c r="R23" t="n">
-        <v>6320924</v>
+        <v>6320904</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3345,10 +3333,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841954</v>
+        <v>122842080</v>
       </c>
       <c r="B24" t="n">
-        <v>90972</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3357,42 +3345,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584450</v>
+        <v>584434</v>
       </c>
       <c r="R24" t="n">
-        <v>6321001</v>
+        <v>6320937</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3439,22 +3423,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122842080</v>
+        <v>122840491</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3463,38 +3447,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584434</v>
+        <v>584478</v>
       </c>
       <c r="R25" t="n">
-        <v>6320937</v>
+        <v>6320912</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3541,22 +3525,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840605</v>
+        <v>122841582</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,20 +3570,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584384</v>
+        <v>584345</v>
       </c>
       <c r="R26" t="n">
-        <v>6320873</v>
+        <v>6320948</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3643,22 +3641,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851479</v>
+        <v>122851540</v>
       </c>
       <c r="B27" t="n">
-        <v>58156</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3667,39 +3665,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3707,10 +3701,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584584</v>
+        <v>584425</v>
       </c>
       <c r="R27" t="n">
-        <v>6320910</v>
+        <v>6320900</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3761,6 +3755,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3779,10 +3774,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851662</v>
+        <v>122851927</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3814,7 +3809,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3827,10 +3822,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584391</v>
+        <v>584411</v>
       </c>
       <c r="R28" t="n">
-        <v>6320923</v>
+        <v>6320904</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3900,10 +3895,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851716</v>
+        <v>122851599</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3948,10 +3943,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584419</v>
+        <v>584395</v>
       </c>
       <c r="R29" t="n">
-        <v>6320935</v>
+        <v>6320916</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4021,10 +4016,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851599</v>
+        <v>122851662</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4056,7 +4051,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4069,10 +4064,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584395</v>
+        <v>584391</v>
       </c>
       <c r="R30" t="n">
-        <v>6320916</v>
+        <v>6320923</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4142,10 +4137,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851862</v>
+        <v>122840279</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4154,49 +4149,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584360</v>
+        <v>584419</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320836</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4223,50 +4214,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851562</v>
+        <v>122840605</v>
       </c>
       <c r="B32" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4275,49 +4255,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R32" t="n">
-        <v>6320915</v>
+        <v>6320873</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4344,50 +4316,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851575</v>
+        <v>122841088</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4419,26 +4380,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584415</v>
+        <v>584332</v>
       </c>
       <c r="R33" t="n">
-        <v>6320915</v>
+        <v>6320935</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4465,50 +4432,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122839339</v>
+        <v>122851623</v>
       </c>
       <c r="B34" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4517,41 +4473,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584548</v>
+        <v>584406</v>
       </c>
       <c r="R34" t="n">
-        <v>6320905</v>
+        <v>6320924</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4578,39 +4542,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122839920</v>
+        <v>122851783</v>
       </c>
       <c r="B35" t="n">
-        <v>95136</v>
+        <v>57372</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4619,41 +4594,53 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584525</v>
+        <v>584336</v>
       </c>
       <c r="R35" t="n">
-        <v>6320880</v>
+        <v>6320920</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4680,14 +4667,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4702,22 +4694,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841596</v>
+        <v>122851479</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>58159</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4726,20 +4718,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4747,20 +4739,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R36" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4787,14 +4791,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4809,12 +4818,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4824,7 +4833,7 @@
         <v>122852003</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4945,10 +4954,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851623</v>
+        <v>122851735</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4980,7 +4989,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4993,10 +5002,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584406</v>
+        <v>584357</v>
       </c>
       <c r="R38" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5066,10 +5075,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851590</v>
+        <v>122851605</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5078,30 +5087,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5114,10 +5123,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584409</v>
+        <v>584395</v>
       </c>
       <c r="R39" t="n">
-        <v>6320920</v>
+        <v>6320916</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5187,10 +5196,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122852007</v>
+        <v>122841878</v>
       </c>
       <c r="B40" t="n">
-        <v>57484</v>
+        <v>105474</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5199,53 +5208,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584646</v>
+        <v>584427</v>
       </c>
       <c r="R40" t="n">
-        <v>6320922</v>
+        <v>6320982</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5272,19 +5269,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5299,22 +5286,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851756</v>
+        <v>122851640</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5323,30 +5310,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5359,10 +5346,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584359</v>
+        <v>584396</v>
       </c>
       <c r="R41" t="n">
-        <v>6320919</v>
+        <v>6320930</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5432,10 +5419,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841518</v>
+        <v>122839339</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5444,55 +5431,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584376</v>
+        <v>584548</v>
       </c>
       <c r="R42" t="n">
-        <v>6320937</v>
+        <v>6320905</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5548,10 +5521,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840279</v>
+        <v>122841596</v>
       </c>
       <c r="B43" t="n">
-        <v>105471</v>
+        <v>57497</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5560,42 +5533,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584419</v>
+        <v>584389</v>
       </c>
       <c r="R43" t="n">
-        <v>6320836</v>
+        <v>6320931</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5628,6 +5597,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5654,10 +5628,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841912</v>
+        <v>122841533</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5687,34 +5661,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584384</v>
+        <v>584369</v>
       </c>
       <c r="R44" t="n">
-        <v>6320970</v>
+        <v>6320926</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5744,6 +5704,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5758,22 +5723,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851504</v>
+        <v>122841912</v>
       </c>
       <c r="B45" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5782,45 +5747,55 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584532</v>
+        <v>584384</v>
       </c>
       <c r="R45" t="n">
-        <v>6320881</v>
+        <v>6320970</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5847,50 +5822,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851640</v>
+        <v>122851741</v>
       </c>
       <c r="B46" t="n">
-        <v>105471</v>
+        <v>57851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5903,21 +5867,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5925,9 +5889,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5935,10 +5903,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584396</v>
+        <v>584357</v>
       </c>
       <c r="R46" t="n">
-        <v>6320930</v>
+        <v>6320937</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5989,7 +5957,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6008,10 +5975,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851605</v>
+        <v>122851504</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>95139</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6024,28 +5991,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -6056,10 +6019,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584395</v>
+        <v>584532</v>
       </c>
       <c r="R47" t="n">
-        <v>6320916</v>
+        <v>6320881</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6129,10 +6092,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841582</v>
+        <v>122851829</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6164,32 +6127,26 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584345</v>
+        <v>584348</v>
       </c>
       <c r="R48" t="n">
-        <v>6320948</v>
+        <v>6320915</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6216,39 +6173,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122839190</v>
+        <v>122851575</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6278,20 +6246,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584581</v>
+        <v>584415</v>
       </c>
       <c r="R49" t="n">
-        <v>6320913</v>
+        <v>6320915</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6318,39 +6294,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841878</v>
+        <v>122851562</v>
       </c>
       <c r="B50" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6380,20 +6367,28 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584427</v>
+        <v>584415</v>
       </c>
       <c r="R50" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6420,39 +6415,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851741</v>
+        <v>122840797</v>
       </c>
       <c r="B51" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6461,53 +6467,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584357</v>
+        <v>584406</v>
       </c>
       <c r="R51" t="n">
-        <v>6320937</v>
+        <v>6320860</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6534,19 +6528,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6561,12 +6545,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6576,7 +6560,7 @@
         <v>122841855</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6675,10 +6659,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851869</v>
+        <v>122851862</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6710,7 +6694,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6723,10 +6707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584360</v>
       </c>
       <c r="R53" t="n">
-        <v>6320904</v>
+        <v>6320915</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6796,10 +6780,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851829</v>
+        <v>122851724</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6831,7 +6815,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6844,10 +6828,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584348</v>
+        <v>584375</v>
       </c>
       <c r="R54" t="n">
-        <v>6320915</v>
+        <v>6320924</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6917,10 +6901,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851469</v>
+        <v>122841518</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6952,26 +6936,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584584</v>
+        <v>584376</v>
       </c>
       <c r="R55" t="n">
-        <v>6320910</v>
+        <v>6320937</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6998,50 +6988,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851811</v>
+        <v>122852007</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>57487</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7050,35 +7029,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7086,10 +7069,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584350</v>
+        <v>584646</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320922</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7140,7 +7123,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7159,10 +7141,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841069</v>
+        <v>122841954</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>90975</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7171,41 +7153,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584349</v>
+        <v>584450</v>
       </c>
       <c r="R57" t="n">
-        <v>6320925</v>
+        <v>6321001</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7235,11 +7221,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7254,22 +7235,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841088</v>
+        <v>122851756</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7301,32 +7282,26 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584332</v>
+        <v>584359</v>
       </c>
       <c r="R58" t="n">
-        <v>6320935</v>
+        <v>6320919</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7353,39 +7328,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841533</v>
+        <v>122851590</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7415,20 +7401,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584369</v>
+        <v>584409</v>
       </c>
       <c r="R59" t="n">
-        <v>6320926</v>
+        <v>6320920</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7455,14 +7449,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7471,28 +7470,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851927</v>
+        <v>122851716</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584411</v>
+        <v>584419</v>
       </c>
       <c r="R60" t="n">
-        <v>6320904</v>
+        <v>6320935</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122839920</v>
+        <v>122841533</v>
       </c>
       <c r="B16" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2452,25 +2452,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R16" t="n">
-        <v>6320880</v>
+        <v>6320926</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2547,10 +2547,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122839190</v>
+        <v>122851756</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2580,20 +2580,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584581</v>
+        <v>584359</v>
       </c>
       <c r="R17" t="n">
-        <v>6320913</v>
+        <v>6320919</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2620,39 +2628,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841409</v>
+        <v>122841855</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2661,46 +2680,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R18" t="n">
-        <v>6320921</v>
+        <v>6320986</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2756,10 +2770,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851469</v>
+        <v>122851724</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2791,7 +2805,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2804,10 +2818,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584584</v>
+        <v>584375</v>
       </c>
       <c r="R19" t="n">
-        <v>6320910</v>
+        <v>6320924</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2877,10 +2891,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841328</v>
+        <v>122841088</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2910,20 +2924,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584336</v>
+        <v>584332</v>
       </c>
       <c r="R20" t="n">
-        <v>6320932</v>
+        <v>6320935</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2953,11 +2981,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,22 +2995,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841069</v>
+        <v>122841328</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3024,10 +3047,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584349</v>
+        <v>584336</v>
       </c>
       <c r="R21" t="n">
-        <v>6320925</v>
+        <v>6320932</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3064,7 +3087,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>50-tal plantor</t>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3091,10 +3114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851811</v>
+        <v>122841878</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3103,49 +3126,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584350</v>
+        <v>584427</v>
       </c>
       <c r="R22" t="n">
-        <v>6320916</v>
+        <v>6320982</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3172,50 +3187,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851869</v>
+        <v>122841912</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3247,26 +3251,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584369</v>
+        <v>584384</v>
       </c>
       <c r="R23" t="n">
-        <v>6320904</v>
+        <v>6320970</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3293,50 +3303,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122842080</v>
+        <v>122851735</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3366,20 +3365,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584434</v>
+        <v>584357</v>
       </c>
       <c r="R24" t="n">
         <v>6320937</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3406,39 +3413,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840491</v>
+        <v>122851811</v>
       </c>
       <c r="B25" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,41 +3465,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584478</v>
+        <v>584350</v>
       </c>
       <c r="R25" t="n">
-        <v>6320912</v>
+        <v>6320916</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3508,39 +3534,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841582</v>
+        <v>122851741</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3549,55 +3586,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584345</v>
+        <v>584357</v>
       </c>
       <c r="R26" t="n">
-        <v>6320948</v>
+        <v>6320937</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3624,9 +3659,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,22 +3686,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851540</v>
+        <v>122841954</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3665,49 +3710,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584425</v>
+        <v>584450</v>
       </c>
       <c r="R27" t="n">
-        <v>6320900</v>
+        <v>6321001</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3734,50 +3775,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851927</v>
+        <v>122840491</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3786,49 +3816,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584411</v>
+        <v>584478</v>
       </c>
       <c r="R28" t="n">
-        <v>6320904</v>
+        <v>6320912</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3855,50 +3877,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851599</v>
+        <v>122839920</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3907,49 +3918,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584395</v>
+        <v>584525</v>
       </c>
       <c r="R29" t="n">
-        <v>6320916</v>
+        <v>6320880</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3976,19 +3979,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3997,29 +3995,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851662</v>
+        <v>122851829</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4051,7 +4048,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4064,10 +4061,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584391</v>
+        <v>584348</v>
       </c>
       <c r="R30" t="n">
-        <v>6320923</v>
+        <v>6320915</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4137,10 +4134,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840279</v>
+        <v>122841409</v>
       </c>
       <c r="B31" t="n">
-        <v>105474</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4149,30 +4146,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4181,13 +4179,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584419</v>
+        <v>584384</v>
       </c>
       <c r="R31" t="n">
-        <v>6320836</v>
+        <v>6320921</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4243,10 +4241,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122840605</v>
+        <v>122851590</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4276,20 +4274,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584384</v>
+        <v>584409</v>
       </c>
       <c r="R32" t="n">
-        <v>6320873</v>
+        <v>6320920</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4316,39 +4322,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841088</v>
+        <v>122842080</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4378,31 +4395,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584332</v>
+        <v>584434</v>
       </c>
       <c r="R33" t="n">
-        <v>6320935</v>
+        <v>6320937</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4449,22 +4452,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851623</v>
+        <v>122840797</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4494,28 +4497,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>584406</v>
       </c>
       <c r="R34" t="n">
-        <v>6320924</v>
+        <v>6320860</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4542,50 +4537,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851783</v>
+        <v>122851623</v>
       </c>
       <c r="B35" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,39 +4578,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4634,10 +4614,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584336</v>
+        <v>584406</v>
       </c>
       <c r="R35" t="n">
-        <v>6320920</v>
+        <v>6320924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4688,6 +4668,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4706,10 +4687,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851479</v>
+        <v>122851640</v>
       </c>
       <c r="B36" t="n">
-        <v>58159</v>
+        <v>105476</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4722,35 +4703,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4758,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584584</v>
+        <v>584396</v>
       </c>
       <c r="R36" t="n">
-        <v>6320910</v>
+        <v>6320930</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4812,6 +4789,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4830,10 +4808,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122852003</v>
+        <v>122851869</v>
       </c>
       <c r="B37" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4842,39 +4820,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4882,10 +4856,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584646</v>
+        <v>584369</v>
       </c>
       <c r="R37" t="n">
-        <v>6320922</v>
+        <v>6320904</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4936,6 +4910,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4954,10 +4929,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851735</v>
+        <v>122851605</v>
       </c>
       <c r="B38" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4966,30 +4941,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5002,10 +4977,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584357</v>
+        <v>584395</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5075,10 +5050,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851605</v>
+        <v>122839339</v>
       </c>
       <c r="B39" t="n">
-        <v>105474</v>
+        <v>95141</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5091,45 +5066,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584395</v>
+        <v>584548</v>
       </c>
       <c r="R39" t="n">
-        <v>6320916</v>
+        <v>6320905</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5156,50 +5123,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841878</v>
+        <v>122841069</v>
       </c>
       <c r="B40" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5208,41 +5164,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584427</v>
+        <v>584349</v>
       </c>
       <c r="R40" t="n">
-        <v>6320982</v>
+        <v>6320925</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5272,6 +5228,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5298,10 +5259,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851640</v>
+        <v>122841582</v>
       </c>
       <c r="B41" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5310,49 +5271,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584396</v>
+        <v>584345</v>
       </c>
       <c r="R41" t="n">
-        <v>6320930</v>
+        <v>6320948</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5379,50 +5346,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122839339</v>
+        <v>122851504</v>
       </c>
       <c r="B42" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5453,19 +5409,23 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584548</v>
+        <v>584532</v>
       </c>
       <c r="R42" t="n">
-        <v>6320905</v>
+        <v>6320881</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5492,39 +5452,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122841596</v>
+        <v>122851469</v>
       </c>
       <c r="B43" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5533,41 +5504,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R43" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5594,14 +5573,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5610,28 +5594,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841533</v>
+        <v>122839190</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5668,10 +5653,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584369</v>
+        <v>584581</v>
       </c>
       <c r="R44" t="n">
-        <v>6320926</v>
+        <v>6320913</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5704,11 +5689,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5735,10 +5715,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841912</v>
+        <v>122840605</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5768,34 +5748,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>584384</v>
       </c>
       <c r="R45" t="n">
-        <v>6320970</v>
+        <v>6320873</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5839,22 +5805,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851741</v>
+        <v>122851540</v>
       </c>
       <c r="B46" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5863,39 +5829,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5903,10 +5865,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584357</v>
+        <v>584425</v>
       </c>
       <c r="R46" t="n">
-        <v>6320937</v>
+        <v>6320900</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5957,6 +5919,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5975,10 +5938,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851504</v>
+        <v>122851479</v>
       </c>
       <c r="B47" t="n">
-        <v>95139</v>
+        <v>58159</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5991,27 +5954,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6019,10 +5990,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584532</v>
+        <v>584584</v>
       </c>
       <c r="R47" t="n">
-        <v>6320881</v>
+        <v>6320910</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6073,7 +6044,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6092,10 +6062,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851829</v>
+        <v>122851716</v>
       </c>
       <c r="B48" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6127,7 +6097,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6140,10 +6110,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R48" t="n">
-        <v>6320915</v>
+        <v>6320935</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6213,10 +6183,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851575</v>
+        <v>122841596</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6225,49 +6195,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584415</v>
+        <v>584389</v>
       </c>
       <c r="R49" t="n">
-        <v>6320915</v>
+        <v>6320931</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6294,19 +6256,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6315,29 +6272,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851562</v>
+        <v>122851783</v>
       </c>
       <c r="B50" t="n">
-        <v>105474</v>
+        <v>57372</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6346,35 +6302,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6382,10 +6342,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584415</v>
+        <v>584336</v>
       </c>
       <c r="R50" t="n">
-        <v>6320915</v>
+        <v>6320920</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6436,7 +6396,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6455,10 +6414,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122840797</v>
+        <v>122851927</v>
       </c>
       <c r="B51" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6488,20 +6447,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584406</v>
+        <v>584411</v>
       </c>
       <c r="R51" t="n">
-        <v>6320860</v>
+        <v>6320904</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6528,39 +6495,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841855</v>
+        <v>122841518</v>
       </c>
       <c r="B52" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6590,20 +6568,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584419</v>
+        <v>584376</v>
       </c>
       <c r="R52" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6647,22 +6639,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851862</v>
+        <v>122851599</v>
       </c>
       <c r="B53" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6694,7 +6686,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6707,10 +6699,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584360</v>
+        <v>584395</v>
       </c>
       <c r="R53" t="n">
-        <v>6320915</v>
+        <v>6320916</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6780,10 +6772,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851724</v>
+        <v>122851862</v>
       </c>
       <c r="B54" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6815,7 +6807,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6828,10 +6820,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584375</v>
+        <v>584360</v>
       </c>
       <c r="R54" t="n">
-        <v>6320924</v>
+        <v>6320915</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6901,10 +6893,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841518</v>
+        <v>122851575</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6936,32 +6928,26 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R55" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6988,39 +6974,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122852007</v>
+        <v>122851662</v>
       </c>
       <c r="B56" t="n">
-        <v>57487</v>
+        <v>98370</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7029,39 +7026,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7069,10 +7062,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584646</v>
+        <v>584391</v>
       </c>
       <c r="R56" t="n">
-        <v>6320922</v>
+        <v>6320923</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7123,6 +7116,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7141,10 +7135,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841954</v>
+        <v>122851562</v>
       </c>
       <c r="B57" t="n">
-        <v>90975</v>
+        <v>105476</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7153,45 +7147,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584450</v>
+        <v>584415</v>
       </c>
       <c r="R57" t="n">
-        <v>6321001</v>
+        <v>6320915</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7218,39 +7216,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851756</v>
+        <v>122840279</v>
       </c>
       <c r="B58" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,49 +7268,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584359</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320919</v>
+        <v>6320836</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7328,50 +7333,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851590</v>
+        <v>122852003</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7380,35 +7374,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7416,10 +7414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584409</v>
+        <v>584646</v>
       </c>
       <c r="R59" t="n">
-        <v>6320920</v>
+        <v>6320922</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7470,7 +7468,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7489,10 +7486,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851716</v>
+        <v>122852007</v>
       </c>
       <c r="B60" t="n">
-        <v>98368</v>
+        <v>57487</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7501,35 +7498,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7537,10 +7538,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584419</v>
+        <v>584646</v>
       </c>
       <c r="R60" t="n">
-        <v>6320935</v>
+        <v>6320922</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7591,7 +7592,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -4013,10 +4013,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851829</v>
+        <v>122841409</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>57372</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4025,46 +4025,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584348</v>
+        <v>584384</v>
       </c>
       <c r="R30" t="n">
-        <v>6320915</v>
+        <v>6320921</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4094,50 +4091,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122841409</v>
+        <v>122851829</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4146,43 +4132,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584384</v>
+        <v>584348</v>
       </c>
       <c r="R31" t="n">
-        <v>6320921</v>
+        <v>6320915</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4212,29 +4201,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840797</v>
+        <v>122851623</v>
       </c>
       <c r="B34" t="n">
         <v>98370</v>
@@ -4497,20 +4497,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>584406</v>
       </c>
       <c r="R34" t="n">
-        <v>6320860</v>
+        <v>6320924</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4537,36 +4545,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851623</v>
+        <v>122840797</v>
       </c>
       <c r="B35" t="n">
         <v>98370</v>
@@ -4599,28 +4618,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
         <v>584406</v>
       </c>
       <c r="R35" t="n">
-        <v>6320924</v>
+        <v>6320860</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4647,40 +4658,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851479</v>
+        <v>122851783</v>
       </c>
       <c r="B47" t="n">
-        <v>58159</v>
+        <v>57372</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5950,20 +5950,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -5990,10 +5990,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584584</v>
+        <v>584336</v>
       </c>
       <c r="R47" t="n">
-        <v>6320910</v>
+        <v>6320920</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851716</v>
+        <v>122841596</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6074,49 +6074,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584419</v>
+        <v>584389</v>
       </c>
       <c r="R48" t="n">
-        <v>6320935</v>
+        <v>6320931</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6143,19 +6135,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6164,29 +6151,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841596</v>
+        <v>122851479</v>
       </c>
       <c r="B49" t="n">
-        <v>57497</v>
+        <v>58159</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6195,20 +6181,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6216,20 +6202,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R49" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6256,14 +6254,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6278,22 +6281,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851783</v>
+        <v>122851716</v>
       </c>
       <c r="B50" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6302,39 +6305,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6342,10 +6341,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584336</v>
+        <v>584419</v>
       </c>
       <c r="R50" t="n">
-        <v>6320920</v>
+        <v>6320935</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6396,6 +6395,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6509-2020 artfynd.xlsx
+++ b/artfynd/A 6509-2020 artfynd.xlsx
@@ -2440,10 +2440,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122841533</v>
+        <v>122851590</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2473,20 +2473,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584369</v>
+        <v>584409</v>
       </c>
       <c r="R16" t="n">
-        <v>6320926</v>
+        <v>6320920</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,14 +2521,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,28 +2542,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851756</v>
+        <v>122842080</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2580,28 +2594,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584359</v>
+        <v>584434</v>
       </c>
       <c r="R17" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2628,50 +2634,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841855</v>
+        <v>122851735</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2701,20 +2696,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584419</v>
+        <v>584357</v>
       </c>
       <c r="R18" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2741,39 +2744,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851724</v>
+        <v>122851662</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,7 +2819,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2818,10 +2832,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584375</v>
+        <v>584391</v>
       </c>
       <c r="R19" t="n">
-        <v>6320924</v>
+        <v>6320923</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2891,10 +2905,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841088</v>
+        <v>122851829</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2926,32 +2940,26 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584332</v>
+        <v>584348</v>
       </c>
       <c r="R20" t="n">
-        <v>6320935</v>
+        <v>6320915</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2978,39 +2986,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841328</v>
+        <v>122851540</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3040,20 +3059,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R21" t="n">
-        <v>6320932</v>
+        <v>6320900</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,14 +3107,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3096,28 +3128,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841878</v>
+        <v>122851927</v>
       </c>
       <c r="B22" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3126,41 +3159,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584427</v>
+        <v>584411</v>
       </c>
       <c r="R22" t="n">
-        <v>6320982</v>
+        <v>6320904</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3187,39 +3228,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841912</v>
+        <v>122841855</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3249,31 +3301,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R23" t="n">
-        <v>6320970</v>
+        <v>6320986</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3320,22 +3358,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851735</v>
+        <v>122851869</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3367,7 +3405,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3380,10 +3418,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584357</v>
+        <v>584369</v>
       </c>
       <c r="R24" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3453,10 +3491,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851811</v>
+        <v>122851756</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3488,7 +3526,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3501,10 +3539,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584350</v>
+        <v>584359</v>
       </c>
       <c r="R25" t="n">
-        <v>6320916</v>
+        <v>6320919</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3574,10 +3612,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851741</v>
+        <v>122851469</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,39 +3624,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3626,10 +3660,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584357</v>
+        <v>584584</v>
       </c>
       <c r="R26" t="n">
-        <v>6320937</v>
+        <v>6320910</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3680,6 +3714,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3698,10 +3733,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841954</v>
+        <v>122841518</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3710,30 +3745,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3742,10 +3787,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584450</v>
+        <v>584376</v>
       </c>
       <c r="R27" t="n">
-        <v>6321001</v>
+        <v>6320937</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3804,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840491</v>
+        <v>122841088</v>
       </c>
       <c r="B28" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3816,38 +3861,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584478</v>
+        <v>584332</v>
       </c>
       <c r="R28" t="n">
-        <v>6320912</v>
+        <v>6320935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3906,10 +3965,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122839920</v>
+        <v>122840279</v>
       </c>
       <c r="B29" t="n">
-        <v>95141</v>
+        <v>105482</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3922,34 +3981,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584525</v>
+        <v>584419</v>
       </c>
       <c r="R29" t="n">
-        <v>6320880</v>
+        <v>6320836</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3982,11 +4045,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4013,10 +4071,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841409</v>
+        <v>122851562</v>
       </c>
       <c r="B30" t="n">
-        <v>57372</v>
+        <v>105482</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4025,43 +4083,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584384</v>
+        <v>584415</v>
       </c>
       <c r="R30" t="n">
-        <v>6320921</v>
+        <v>6320915</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4091,39 +4152,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851829</v>
+        <v>122851811</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4155,7 +4227,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4168,10 +4240,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584348</v>
+        <v>584350</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320916</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4241,10 +4313,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851590</v>
+        <v>122852007</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>57487</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4253,35 +4325,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4289,10 +4365,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584409</v>
+        <v>584646</v>
       </c>
       <c r="R32" t="n">
-        <v>6320920</v>
+        <v>6320922</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4343,7 +4419,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4362,10 +4437,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122842080</v>
+        <v>122841582</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4395,20 +4470,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584434</v>
+        <v>584345</v>
       </c>
       <c r="R33" t="n">
-        <v>6320937</v>
+        <v>6320948</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4452,12 +4541,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4467,7 +4556,7 @@
         <v>122851623</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4585,10 +4674,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122840797</v>
+        <v>122851724</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4618,20 +4707,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584406</v>
+        <v>584375</v>
       </c>
       <c r="R35" t="n">
-        <v>6320860</v>
+        <v>6320924</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4658,39 +4755,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851640</v>
+        <v>122851504</v>
       </c>
       <c r="B36" t="n">
-        <v>105476</v>
+        <v>95147</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4703,28 +4811,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -4735,10 +4839,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584396</v>
+        <v>584532</v>
       </c>
       <c r="R36" t="n">
-        <v>6320930</v>
+        <v>6320881</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4808,10 +4912,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851869</v>
+        <v>122852003</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4820,35 +4924,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4856,10 +4964,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584369</v>
+        <v>584646</v>
       </c>
       <c r="R37" t="n">
-        <v>6320904</v>
+        <v>6320922</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4910,7 +5018,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4929,10 +5036,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851605</v>
+        <v>122851862</v>
       </c>
       <c r="B38" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4941,30 +5048,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4977,10 +5084,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584395</v>
+        <v>584360</v>
       </c>
       <c r="R38" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5050,10 +5157,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122839339</v>
+        <v>122840797</v>
       </c>
       <c r="B39" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5062,41 +5169,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584548</v>
+        <v>584406</v>
       </c>
       <c r="R39" t="n">
-        <v>6320905</v>
+        <v>6320860</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5152,10 +5259,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841069</v>
+        <v>122851640</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5164,41 +5271,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584349</v>
+        <v>584396</v>
       </c>
       <c r="R40" t="n">
-        <v>6320925</v>
+        <v>6320930</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5225,14 +5340,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5241,28 +5361,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841582</v>
+        <v>122841878</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5271,52 +5392,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584345</v>
+        <v>584427</v>
       </c>
       <c r="R41" t="n">
-        <v>6320948</v>
+        <v>6320982</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5363,22 +5470,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851504</v>
+        <v>122841533</v>
       </c>
       <c r="B42" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5387,45 +5494,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584532</v>
+        <v>584369</v>
       </c>
       <c r="R42" t="n">
-        <v>6320881</v>
+        <v>6320926</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5452,19 +5555,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5473,29 +5571,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851469</v>
+        <v>122841954</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>90983</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5504,49 +5601,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584584</v>
+        <v>584450</v>
       </c>
       <c r="R43" t="n">
-        <v>6320910</v>
+        <v>6321001</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5573,50 +5666,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122839190</v>
+        <v>122851783</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>57372</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5625,41 +5707,53 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584581</v>
+        <v>584336</v>
       </c>
       <c r="R44" t="n">
-        <v>6320913</v>
+        <v>6320920</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5686,9 +5780,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,22 +5807,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840605</v>
+        <v>122841069</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5755,13 +5859,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584384</v>
+        <v>584349</v>
       </c>
       <c r="R45" t="n">
-        <v>6320873</v>
+        <v>6320925</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5791,6 +5895,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5817,10 +5926,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851540</v>
+        <v>122851599</v>
       </c>
       <c r="B46" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5852,7 +5961,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5865,10 +5974,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584425</v>
+        <v>584395</v>
       </c>
       <c r="R46" t="n">
-        <v>6320900</v>
+        <v>6320916</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5938,10 +6047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851783</v>
+        <v>122851575</v>
       </c>
       <c r="B47" t="n">
-        <v>57372</v>
+        <v>98376</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5950,39 +6059,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5990,10 +6095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584336</v>
+        <v>584415</v>
       </c>
       <c r="R47" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6044,6 +6149,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6062,10 +6168,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841596</v>
+        <v>122851741</v>
       </c>
       <c r="B48" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6074,20 +6180,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6095,20 +6201,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584389</v>
+        <v>584357</v>
       </c>
       <c r="R48" t="n">
-        <v>6320931</v>
+        <v>6320937</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6135,14 +6253,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6157,22 +6280,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851479</v>
+        <v>122841328</v>
       </c>
       <c r="B49" t="n">
-        <v>58159</v>
+        <v>98376</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6181,53 +6304,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584584</v>
+        <v>584336</v>
       </c>
       <c r="R49" t="n">
-        <v>6320910</v>
+        <v>6320932</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6254,19 +6365,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6281,12 +6387,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6296,7 +6402,7 @@
         <v>122851716</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6414,10 +6520,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851927</v>
+        <v>122840491</v>
       </c>
       <c r="B51" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6426,49 +6532,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584411</v>
+        <v>584478</v>
       </c>
       <c r="R51" t="n">
-        <v>6320904</v>
+        <v>6320912</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6495,50 +6593,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841518</v>
+        <v>122840605</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6568,31 +6655,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584376</v>
+        <v>584384</v>
       </c>
       <c r="R52" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6639,22 +6712,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851599</v>
+        <v>122839339</v>
       </c>
       <c r="B53" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6663,49 +6736,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584395</v>
+        <v>584548</v>
       </c>
       <c r="R53" t="n">
-        <v>6320916</v>
+        <v>6320905</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6732,50 +6797,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851862</v>
+        <v>122841596</v>
       </c>
       <c r="B54" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6784,49 +6838,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584360</v>
+        <v>584389</v>
       </c>
       <c r="R54" t="n">
-        <v>6320915</v>
+        <v>6320931</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6853,19 +6899,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6874,29 +6915,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851575</v>
+        <v>122839190</v>
       </c>
       <c r="B55" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6926,28 +6966,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584415</v>
+        <v>584581</v>
       </c>
       <c r="R55" t="n">
-        <v>6320915</v>
+        <v>6320913</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6974,50 +7006,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851662</v>
+        <v>122841409</v>
       </c>
       <c r="B56" t="n">
-        <v>98370</v>
+        <v>57372</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7026,46 +7047,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584391</v>
+        <v>584384</v>
       </c>
       <c r="R56" t="n">
-        <v>6320923</v>
+        <v>6320921</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7095,50 +7113,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851562</v>
+        <v>122841912</v>
       </c>
       <c r="B57" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7147,49 +7154,55 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R57" t="n">
-        <v>6320915</v>
+        <v>6320970</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7216,50 +7229,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840279</v>
+        <v>122851479</v>
       </c>
       <c r="B58" t="n">
-        <v>105476</v>
+        <v>58159</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7272,41 +7274,49 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>103044</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R58" t="n">
-        <v>6320836</v>
+        <v>6320910</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7333,9 +7343,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7350,22 +7370,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122852003</v>
+        <v>122839920</v>
       </c>
       <c r="B59" t="n">
-        <v>57497</v>
+        <v>95147</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7374,53 +7394,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584646</v>
+        <v>584525</v>
       </c>
       <c r="R59" t="n">
-        <v>6320922</v>
+        <v>6320880</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7447,19 +7455,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7474,22 +7477,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122852007</v>
+        <v>122851605</v>
       </c>
       <c r="B60" t="n">
-        <v>57487</v>
+        <v>105482</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7498,39 +7501,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7538,10 +7537,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584646</v>
+        <v>584395</v>
       </c>
       <c r="R60" t="n">
-        <v>6320922</v>
+        <v>6320916</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7592,6 +7591,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
